--- a/BAAY_PROJECTS_LIMITED_Master_Workbook_2023_2025.xlsx
+++ b/BAAY_PROJECTS_LIMITED_Master_Workbook_2023_2025.xlsx
@@ -190,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -261,39 +261,49 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -11501,38 +11511,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="98" customWidth="1" min="1" max="1"/>
-    <col width="56" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="102" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
-    <col width="25" customWidth="1" min="13" max="13"/>
-    <col width="37" customWidth="1" min="14" max="14"/>
-    <col width="35" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="37" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="29" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BAAY PROJECTS LIMITED — COMPREHENSIVE PROJECT REGISTER</t>
+          <t>BAAY PROJECTS LIMITED — COMPREHENSIVE PROJECT &amp; ESTATE REGISTER</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Civil Engineering, Land Resale, Joint Venture Real Estate &amp; Consultancy Portfolio (2023 - 2025)</t>
+          <t>Real Estate Development, Land Subdivisions, Luxury Housing &amp; Infrastructure Portfolio (2022 - 2025)</t>
         </is>
       </c>
     </row>
@@ -11550,37 +11560,37 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Project Type</t>
+          <t>Product Line</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Landowner / Client</t>
+          <t>Subscribers (Count)</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Legal Rights &amp; Contract Basis</t>
+          <t>Contract Basis &amp; Title Stage</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Contract Value (NGN)</t>
+          <t>Total Contract Value (NGN)</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Commencement</t>
+          <t>Cash Collections (NGN)</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Target Completion</t>
+          <t>Outstanding Client Balance (NGN)</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Progress / Stage (%)</t>
+          <t>IFRS 15 Stage (%)</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -11595,477 +11605,698 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>Billed Revenue (NGN)</t>
+          <t>Cumulative Billed Revenue (NGN)</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>Cash Collections (NGN)</t>
+          <t>Contract Assets / Retentions (NGN)</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>Retentions / Contract Assets (NGN)</t>
+          <t>Contract Liabilities / Advances (NGN)</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>NRV Test / Valuation Status</t>
+          <t>NRV Test Status</t>
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr">
         <is>
-          <t>Risk Assessment</t>
+          <t>Operational Status</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>PROJ-101</t>
+          <t>PRJ-GC01</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Lekki Residential Estate Infrastructure &amp; Civil Works</t>
+          <t>Green City Phase 1 (Lantaba, Ketu-Epe)</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Civil Engineering &amp; Building</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>Apex Properties Ltd</t>
-        </is>
+          <t>Land Development</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="n">
+        <v>45</v>
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>Subcontractor Agreement / Enforceable Right to Payment</t>
+          <t>Registered Survey / Deed of Assignment</t>
         </is>
       </c>
       <c r="F5" s="28" t="n">
-        <v>65000000</v>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>2024-12-31</t>
-        </is>
-      </c>
-      <c r="I5" s="32" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J5" s="22" t="n">
-        <v>40600000</v>
-      </c>
-      <c r="K5" s="22" t="n">
-        <v>2140000</v>
-      </c>
-      <c r="L5" s="22" t="n">
-        <v>60000000</v>
-      </c>
-      <c r="M5" s="22" t="n">
-        <v>56350000</v>
-      </c>
-      <c r="N5" s="22" t="n">
-        <v>3650000</v>
-      </c>
-      <c r="O5" s="12" t="inlineStr">
-        <is>
-          <t>Cost &lt; Recoverable Amount (Pass)</t>
-        </is>
-      </c>
-      <c r="P5" s="30" t="inlineStr">
-        <is>
-          <t>Low / Active Execution</t>
+        <v>224659680</v>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>223449680</v>
+      </c>
+      <c r="H5" s="28" t="n">
+        <v>-290000</v>
+      </c>
+      <c r="I5" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="28" t="n">
+        <v>142500000</v>
+      </c>
+      <c r="K5" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="28" t="n">
+        <v>224659680</v>
+      </c>
+      <c r="M5" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="34" t="inlineStr">
+        <is>
+          <t>Cost &lt; Market Value (Pass)</t>
+        </is>
+      </c>
+      <c r="P5" s="9" t="inlineStr">
+        <is>
+          <t>Completed / Allocated</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>PROJ-102</t>
+          <t>PRJ-GC02</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Ibeju-Lekki Scheme 1 Land Subdivision &amp; Resale</t>
+          <t>Green City Phase 2 (Idobi, Ketu-Epe)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Land Purchase &amp; Resale</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Ibeju Family Land Committee</t>
-        </is>
+          <t>Land Development</t>
+        </is>
+      </c>
+      <c r="D6" s="35" t="n">
+        <v>49</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Deed of Assignment &amp; Registered Survey (20 Plots)</t>
+          <t>Gazette Excision &amp; Perimeter Survey</t>
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>35000000</v>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>2023-02-01</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="I6" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="21" t="n">
-        <v>19900000</v>
-      </c>
-      <c r="K6" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="21" t="n">
-        <v>32000000</v>
-      </c>
-      <c r="M6" s="21" t="n">
-        <v>32000000</v>
-      </c>
-      <c r="N6" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="14" t="inlineStr">
-        <is>
-          <t>Land Sold &gt; Cost (Pass)</t>
-        </is>
-      </c>
-      <c r="P6" s="29" t="inlineStr">
-        <is>
-          <t>Completed / Fully Sold</t>
+        <v>209610000</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>174486400</v>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>33823600</v>
+      </c>
+      <c r="I6" s="36" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J6" s="27" t="n">
+        <v>128000000</v>
+      </c>
+      <c r="K6" s="27" t="n">
+        <v>22500000</v>
+      </c>
+      <c r="L6" s="27" t="n">
+        <v>178168500</v>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>3682100</v>
+      </c>
+      <c r="N6" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="37" t="inlineStr">
+        <is>
+          <t>Cost &lt; Market Value (Pass)</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>Active Development</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>PROJ-103</t>
+          <t>PRJ-GC03</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Ikeja Commercial Office Renovation &amp; Civil Works</t>
+          <t>Green City Phase 3 &amp; Extension (Omu-Epe)</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Commercial Civil Works</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Horizon Holdings Ltd</t>
-        </is>
+          <t>Land Scheme</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="n">
+        <v>43</v>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>Civil Works Contract &amp; Performance Bond</t>
+          <t>Survey Plan &amp; Layout Approval</t>
         </is>
       </c>
       <c r="F7" s="28" t="n">
-        <v>1850000</v>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>2023-03-01</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>2023-12-15</t>
-        </is>
-      </c>
-      <c r="I7" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="22" t="n">
-        <v>11500000</v>
-      </c>
-      <c r="K7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="22" t="n">
-        <v>18500000</v>
-      </c>
-      <c r="M7" s="22" t="n">
-        <v>18500000</v>
-      </c>
-      <c r="N7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="12" t="inlineStr">
-        <is>
-          <t>Completed &amp; Certified (Pass)</t>
-        </is>
-      </c>
-      <c r="P7" s="30" t="inlineStr">
-        <is>
-          <t>Completed / Fully Settled</t>
+        <v>173905000</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>160930000</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>12975000</v>
+      </c>
+      <c r="I7" s="33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J7" s="28" t="n">
+        <v>105000000</v>
+      </c>
+      <c r="K7" s="28" t="n">
+        <v>11600000</v>
+      </c>
+      <c r="L7" s="28" t="n">
+        <v>156514500</v>
+      </c>
+      <c r="M7" s="28" t="n">
+        <v>4415500</v>
+      </c>
+      <c r="N7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="34" t="inlineStr">
+        <is>
+          <t>Cost &lt; Market Value (Pass)</t>
+        </is>
+      </c>
+      <c r="P7" s="9" t="inlineStr">
+        <is>
+          <t>Active Plot Allocation</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>PROJ-104</t>
+          <t>PRJ-GCI</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Victoria Island Luxury Maisonettes Development</t>
+          <t>Green City Ibadan (Akinyele-Moniya)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Joint Venture Real Estate</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>VI Prime Properties &amp; Landowners</t>
-        </is>
+          <t>Regional Land Scheme</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="n">
+        <v>10</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Unincorporated Joint Venture Agreement (40% Profit Share)</t>
+          <t>Registered Survey &amp; Freehold</t>
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>120000000</v>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>2024-03-01</t>
-        </is>
-      </c>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="I8" s="33" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J8" s="21" t="n">
-        <v>45200000</v>
-      </c>
-      <c r="K8" s="21" t="n">
-        <v>55000000</v>
-      </c>
-      <c r="L8" s="21" t="n">
-        <v>48000000</v>
-      </c>
-      <c r="M8" s="21" t="n">
-        <v>42000000</v>
-      </c>
-      <c r="N8" s="21" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="O8" s="14" t="inlineStr">
-        <is>
-          <t>Market Appraisal &gt; Cost (Pass)</t>
-        </is>
-      </c>
-      <c r="P8" s="29" t="inlineStr">
-        <is>
-          <t>Medium / JV Progress</t>
+        <v>30550000</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>25750000</v>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="I8" s="36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J8" s="27" t="n">
+        <v>18500000</v>
+      </c>
+      <c r="K8" s="27" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="L8" s="27" t="n">
+        <v>24440000</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>1310000</v>
+      </c>
+      <c r="N8" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="37" t="inlineStr">
+        <is>
+          <t>Cost &lt; Market Value (Pass)</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>Active Marketing</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>PROJ-105</t>
+          <t>PRJ-PC01</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Epe Mixed-Use Residential Scheme (Phase 1)</t>
+          <t>Pacific Court (Phase 1 &amp; 2)</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Land Subdivision &amp; Infrastructure</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Epe Land Registry / Community</t>
-        </is>
+          <t>Residential Housing</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="n">
+        <v>10</v>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>Perimeter Survey &amp; Governor's Consent In Progress</t>
+          <t>Governor's Consent &amp; Building Approval</t>
         </is>
       </c>
       <c r="F9" s="28" t="n">
-        <v>45000000</v>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>2023-11-01</t>
-        </is>
-      </c>
-      <c r="H9" s="11" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="I9" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J9" s="22" t="n">
-        <v>23500000</v>
-      </c>
-      <c r="K9" s="22" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="L9" s="22" t="n">
-        <v>28000000</v>
-      </c>
-      <c r="M9" s="22" t="n">
-        <v>24500000</v>
-      </c>
-      <c r="N9" s="22" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="O9" s="12" t="inlineStr">
-        <is>
-          <t>Valuation &gt; Cost (Pass)</t>
-        </is>
-      </c>
-      <c r="P9" s="30" t="inlineStr">
-        <is>
-          <t>Low / Strong Demand</t>
+        <v>889200000</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>52500000</v>
+      </c>
+      <c r="H9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="33" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J9" s="28" t="n">
+        <v>480000000</v>
+      </c>
+      <c r="K9" s="28" t="n">
+        <v>258000000</v>
+      </c>
+      <c r="L9" s="28" t="n">
+        <v>577980000</v>
+      </c>
+      <c r="M9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="28" t="n">
+        <v>52500000</v>
+      </c>
+      <c r="O9" s="34" t="inlineStr">
+        <is>
+          <t>Appraisal &gt; Cost (Pass)</t>
+        </is>
+      </c>
+      <c r="P9" s="9" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PROJ-106</t>
+          <t>PRJ-PA01</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Project Management &amp; Structural Consultancy</t>
+          <t>Pacific Apartment (Gbagada / Mainland)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Engineering Consultancy</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Various Corporate Clients</t>
-        </is>
+          <t>Luxury Multi-Family Housing</t>
+        </is>
+      </c>
+      <c r="D10" s="35" t="n">
+        <v>14</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Annual Engineering Retainers &amp; SLA Contracts</t>
+          <t>C of O / Approved Architectural Drawings</t>
         </is>
       </c>
       <c r="F10" s="27" t="n">
-        <v>25000000</v>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="I10" s="33" t="n">
+        <v>1335000000</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>850626141</v>
+      </c>
+      <c r="H10" s="27" t="n">
+        <v>484373859</v>
+      </c>
+      <c r="I10" s="36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J10" s="27" t="n">
+        <v>720000000</v>
+      </c>
+      <c r="K10" s="27" t="n">
+        <v>480000000</v>
+      </c>
+      <c r="L10" s="27" t="n">
+        <v>801000000</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="27" t="n">
+        <v>49626141</v>
+      </c>
+      <c r="O10" s="37" t="inlineStr">
+        <is>
+          <t>Appraisal &gt; Cost (Pass)</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>Active Structural Works</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>PRJ-GVC</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Gorge View Court (GVC Gbagada)</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Premium Housing Estate</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>C of O / Turnkey Joint Development</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="n">
+        <v>540000000</v>
+      </c>
+      <c r="G11" s="28" t="n">
+        <v>530000000</v>
+      </c>
+      <c r="H11" s="28" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I11" s="33" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J11" s="28" t="n">
+        <v>385000000</v>
+      </c>
+      <c r="K11" s="28" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="L11" s="28" t="n">
+        <v>513000000</v>
+      </c>
+      <c r="M11" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="O11" s="34" t="inlineStr">
+        <is>
+          <t>Appraisal &gt; Cost (Pass)</t>
+        </is>
+      </c>
+      <c r="P11" s="9" t="inlineStr">
+        <is>
+          <t>Finishing &amp; Handover</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>PRJ-BF01</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Baay Foreshore (Waterfront Scheme)</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Luxury Waterfront Land &amp; Housing</t>
+        </is>
+      </c>
+      <c r="D12" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Waterfront Excision &amp; Reclamation Approval</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="n">
+        <v>563320000</v>
+      </c>
+      <c r="G12" s="27" t="n">
+        <v>339070000</v>
+      </c>
+      <c r="H12" s="27" t="n">
+        <v>224250000</v>
+      </c>
+      <c r="I12" s="36" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J12" s="27" t="n">
+        <v>290000000</v>
+      </c>
+      <c r="K12" s="27" t="n">
+        <v>237000000</v>
+      </c>
+      <c r="L12" s="27" t="n">
+        <v>309826000</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="27" t="n">
+        <v>29244000</v>
+      </c>
+      <c r="O12" s="37" t="inlineStr">
+        <is>
+          <t>Appraisal &gt; Cost (Pass)</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>Reclamation &amp; Piling</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>PRJ-HG01</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Heritage Garden &amp; Green Hillside / Agbowa</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Residential Land Schemes</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="n">
+        <v>27</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Perimeter Survey &amp; Community Agreement</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="n">
+        <v>50122060</v>
+      </c>
+      <c r="G13" s="28" t="n">
+        <v>45463060</v>
+      </c>
+      <c r="H13" s="28" t="n">
+        <v>4659000</v>
+      </c>
+      <c r="I13" s="33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J13" s="28" t="n">
+        <v>28000000</v>
+      </c>
+      <c r="K13" s="28" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="L13" s="28" t="n">
+        <v>45109854</v>
+      </c>
+      <c r="M13" s="28" t="n">
+        <v>353206</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="34" t="inlineStr">
+        <is>
+          <t>Cost &lt; Market Value (Pass)</t>
+        </is>
+      </c>
+      <c r="P13" s="9" t="inlineStr">
+        <is>
+          <t>Active Plot Allocation</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>PRJ-GEN</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Unallocated Schemes &amp; Ancillary Services</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Development &amp; Ancillary</t>
+        </is>
+      </c>
+      <c r="D14" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Documentation &amp; Corner Piece Premiums</t>
+        </is>
+      </c>
+      <c r="F14" s="27" t="n">
+        <v>8965000</v>
+      </c>
+      <c r="G14" s="27" t="n">
+        <v>8965000</v>
+      </c>
+      <c r="H14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="21" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="K10" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="21" t="n">
-        <v>22700000</v>
-      </c>
-      <c r="M10" s="21" t="n">
-        <v>22700000</v>
-      </c>
-      <c r="N10" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="14" t="inlineStr">
-        <is>
-          <t>Consultancy Services (Pass)</t>
-        </is>
-      </c>
-      <c r="P10" s="29" t="inlineStr">
-        <is>
-          <t>Low / Recurring Cashflow</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>TOTAL ACTIVE PORTFOLIO</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="n"/>
-      <c r="C11" s="31" t="n"/>
-      <c r="D11" s="31" t="n"/>
-      <c r="E11" s="31" t="n"/>
-      <c r="F11" s="24">
-        <f>SUM(F5:F10)</f>
+      <c r="J14" s="27" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="K14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="27" t="n">
+        <v>8965000</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="37" t="inlineStr">
+        <is>
+          <t>Cost &lt; Market Value (Pass)</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="38" t="n"/>
+      <c r="B15" s="39" t="inlineStr">
+        <is>
+          <t>TOTAL PORTFOLIO (2022 - 2025)</t>
+        </is>
+      </c>
+      <c r="C15" s="38" t="n"/>
+      <c r="D15" s="40">
+        <f>SUM(D5:D14)</f>
         <v/>
       </c>
-      <c r="G11" s="31" t="n"/>
-      <c r="H11" s="31" t="n"/>
-      <c r="I11" s="31" t="n"/>
-      <c r="J11" s="24">
-        <f>SUM(J5:J10)</f>
+      <c r="E15" s="38" t="n"/>
+      <c r="F15" s="41">
+        <f>SUM(F5:F14)</f>
         <v/>
       </c>
-      <c r="K11" s="24">
-        <f>SUM(K5:K10)</f>
+      <c r="G15" s="41">
+        <f>SUM(G5:G14)</f>
         <v/>
       </c>
-      <c r="L11" s="24">
-        <f>SUM(L5:L10)</f>
+      <c r="H15" s="41">
+        <f>SUM(H5:H14)</f>
         <v/>
       </c>
-      <c r="M11" s="24">
-        <f>SUM(M5:M10)</f>
+      <c r="I15" s="38" t="n"/>
+      <c r="J15" s="41">
+        <f>SUM(J5:J14)</f>
         <v/>
       </c>
-      <c r="N11" s="24">
-        <f>SUM(N5:N10)</f>
+      <c r="K15" s="41">
+        <f>SUM(K5:K14)</f>
         <v/>
       </c>
-      <c r="O11" s="31" t="n"/>
-      <c r="P11" s="31" t="n"/>
+      <c r="L15" s="41">
+        <f>SUM(L5:L14)</f>
+        <v/>
+      </c>
+      <c r="M15" s="41">
+        <f>SUM(M5:M14)</f>
+        <v/>
+      </c>
+      <c r="N15" s="41">
+        <f>SUM(N5:N14)</f>
+        <v/>
+      </c>
+      <c r="O15" s="38" t="n"/>
+      <c r="P15" s="38" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12078,29 +12309,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="100" customWidth="1" min="6" max="6"/>
-    <col width="133" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BAAY PROJECTS LIMITED — IFRS 15 REVENUE &amp; IAS 2 INVENTORY / WIP MODEL</t>
+          <t>BAAY PROJECTS LIMITED — IFRS 15 REVENUE &amp; IAS 2 WIP RECONCILIATION</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>5-Step Revenue Recognition Evaluation, Contract Assets/Liabilities &amp; IAS 2 Inventory Roll-Forward</t>
+          <t>5-Step Revenue Model, Input Method (Cost-to-Cost) &amp; Development Inventory Valuation (2023 - 2025)</t>
         </is>
       </c>
     </row>
@@ -12108,565 +12339,343 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Revenue / Project Stream</t>
+          <t>Project / Revenue Stream</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>IFRS 15 Timing &amp; Model</t>
+          <t>Revenue Recognition Basis</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>FY 2022 (NGN)</t>
+          <t>Performance Obligation</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>FY 2023 (NGN)</t>
+          <t>2023 Revenue (NGN)</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>FY 2024 (NGN)</t>
+          <t>2024 Revenue (NGN)</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>FY 2025 (NGN)</t>
+          <t>2025 Revenue (NGN)</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Accounting Policy &amp; Recognition Criteria</t>
+          <t>Total Cumulative (NGN)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Civil Engineering &amp; Construction Contracts</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>Over Time (Cost-to-Cost Input Method)</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="22" t="n">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Green City Phase 1 &amp; 2 (Ketu-Epe)</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Point-in-Time (Transfer of Control)</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Plot Allocation &amp; Registered Survey Delivery</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="E5" s="28" t="n">
+        <v>24800000</v>
+      </c>
+      <c r="F5" s="28" t="n">
+        <v>38500000</v>
+      </c>
+      <c r="G5" s="17">
+        <f>SUM(D5:F5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Pacific Court &amp; Pacific Apartment</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Over-Time (Input Cost Method)</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Construction Milestones &amp; Architectural Delivery</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="n">
         <v>22000000</v>
       </c>
-      <c r="E5" s="22" t="n">
-        <v>38000000</v>
-      </c>
-      <c r="F5" s="22" t="n">
-        <v>68000000</v>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>Recognized over time as performance creates/enhances asset controlled by client with enforceable payment rights (IFRS 15.35(b)).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Land Subdivision &amp; Real Estate Sales</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Point in Time (Title Execution / Delivery)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="21" t="n">
+      <c r="E6" s="27" t="n">
+        <v>32500000</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>54000000</v>
+      </c>
+      <c r="G6" s="19">
+        <f>SUM(D6:F6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Gorge View Court &amp; Baay Foreshore</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Over-Time (Input Cost Method)</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Site Reclamation, Piling &amp; Structural Civil Works</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="28" t="n">
         <v>12500000</v>
       </c>
-      <c r="E6" s="21" t="n">
-        <v>19500000</v>
-      </c>
-      <c r="F6" s="21" t="n">
-        <v>32500000</v>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Recognized at point in time when legal deed is executed, physical possession transferred and consideration received/unconditional.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Project Management &amp; Engineering Consulting</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>Over Time (Services Rendered)</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="22" t="n">
+      <c r="G7" s="17">
+        <f>SUM(D7:F7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Green City Ibadan &amp; Heritage Garden</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Point-in-Time (Transfer of Control)</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Plot Allocation &amp; Layout Documentation</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="G8" s="19">
+        <f>SUM(D8:F8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Engineering Consultancy &amp; Project Advisory</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Over-Time (Services Rendered)</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Design, Structural Valuations &amp; Project Supervision</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="n">
         <v>4000000</v>
       </c>
-      <c r="E7" s="22" t="n">
-        <v>6700000</v>
-      </c>
-      <c r="F7" s="22" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>Recognized over time as services are simultaneously received and consumed by client (IFRS 15.35(a)).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>TOTAL REVENUE FROM CONTRACTS WITH CUSTOMERS</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>Full IFRS 15 Framework</t>
-        </is>
-      </c>
-      <c r="C8" s="24">
-        <f>SUM(C5:C7)</f>
+      <c r="E9" s="28" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="G9" s="17">
+        <f>SUM(D9:F9)</f>
         <v/>
       </c>
-      <c r="D8" s="24">
-        <f>SUM(D5:D7)</f>
+    </row>
+    <row r="10">
+      <c r="A10" s="39" t="inlineStr">
+        <is>
+          <t>TOTAL IFRS 15 REVENUE RECOGNIZED</t>
+        </is>
+      </c>
+      <c r="B10" s="38" t="n"/>
+      <c r="C10" s="38" t="n"/>
+      <c r="D10" s="41">
+        <f>SUM(D5:D9)</f>
         <v/>
       </c>
-      <c r="E8" s="24">
-        <f>SUM(E5:E7)</f>
+      <c r="E10" s="41">
+        <f>SUM(E5:E9)</f>
         <v/>
       </c>
-      <c r="F8" s="24">
-        <f>SUM(F5:F7)</f>
+      <c r="F10" s="41">
+        <f>SUM(F5:F9)</f>
         <v/>
       </c>
-      <c r="G8" s="34" t="inlineStr">
-        <is>
-          <t>Gross statutory turnover recognized in Statement of Profit or Loss.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTRACT BALANCES ROLL-FORWARD (IFRS 15)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Contract Balance Category</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>31 Dec 2022 (NGN)</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>31 Dec 2023 (NGN)</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>31 Dec 2024 (NGN)</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>31 Dec 2025 (NGN)</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Accounting Definition &amp; Nature</t>
-        </is>
-      </c>
-    </row>
+      <c r="G10" s="41">
+        <f>SUM(G5:G9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Contract Assets (Unbilled Revenue Certified)</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="22" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="D13" s="22" t="n">
-        <v>4150000</v>
-      </c>
-      <c r="E13" s="22" t="n">
-        <v>6850000</v>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>Cumulative unbilled revenue for performance completed to date exceeding progress billings issued.</t>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>IAS 2 DEVELOPMENT INVENTORIES &amp; WIP SCHEDULE</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Contract Liabilities (Customer Mobilization Advances)</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="21" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="D14" s="21" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="E14" s="21" t="n">
-        <v>5800000</v>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Customer advances and deposits received prior to satisfying performance obligations.</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Inventory Component</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Valuation Standard</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>31-Dec-2022 (NGN)</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>31-Dec-2023 (NGN)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>31-Dec-2024 (NGN)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>31-Dec-2025 (NGN)</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Audit Basis</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>Net Contract Position</t>
-        </is>
-      </c>
-      <c r="B15" s="24">
-        <f>B13-B14</f>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Land Acquired for Subdivision &amp; Resale</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Lower of Cost and NRV</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="28" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="E15" s="28" t="n">
+        <v>8200000</v>
+      </c>
+      <c r="F15" s="28" t="n">
+        <v>14500000</v>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Deed of Purchase &amp; Survey Valuation</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Development Work-in-Progress (WIP)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Direct Cost Incurred (IAS 2.10)</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="27" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="E16" s="27" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>9800000</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Civil Infrastructure &amp; Piling Costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="39" t="inlineStr">
+        <is>
+          <t>TOTAL INVENTORIES &amp; WIP (SFP LINE)</t>
+        </is>
+      </c>
+      <c r="B17" s="38" t="n"/>
+      <c r="C17" s="41">
+        <f>SUM(C15:C16)</f>
         <v/>
       </c>
-      <c r="C15" s="24">
-        <f>C13-C14</f>
+      <c r="D17" s="41">
+        <f>SUM(D15:D16)</f>
         <v/>
       </c>
-      <c r="D15" s="24">
-        <f>D13-D14</f>
+      <c r="E17" s="41">
+        <f>SUM(E15:E16)</f>
         <v/>
       </c>
-      <c r="E15" s="24">
-        <f>E13-E14</f>
+      <c r="F17" s="41">
+        <f>SUM(F15:F16)</f>
         <v/>
       </c>
-      <c r="F15" s="25" t="inlineStr">
-        <is>
-          <t>Net contract asset / (liability) position under IFRS 15.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>IAS 2 DEVELOPMENT INVENTORIES &amp; WORK-IN-PROGRESS ROLL-FORWARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Inventory Component</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Opening Balance 1 Jan (NGN)</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Land &amp; Development Additions (NGN)</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Direct Construction Incurred (NGN)</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Costs Released to Cost of Sales (NGN)</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Closing Balance 31 Dec (NGN)</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>NRV Test Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>FY 2023 — Land Held for Resale (IAS 2)</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="21" t="n">
-        <v>13500000</v>
-      </c>
-      <c r="D20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="21" t="n">
-        <v>-8100000</v>
-      </c>
-      <c r="F20" s="21" t="n">
-        <v>5400000</v>
-      </c>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>PASSED (NRV &gt; Cost)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>FY 2023 — Construction WIP (IAS 2)</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="22" t="n">
-        <v>17450000</v>
-      </c>
-      <c r="E21" s="22" t="n">
-        <v>-14200000</v>
-      </c>
-      <c r="F21" s="22" t="n">
-        <v>3250000</v>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>PASSED (NRV &gt; Cost)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="23" t="inlineStr">
-        <is>
-          <t>FY 2023 — TOTAL INVENTORIES</t>
-        </is>
-      </c>
-      <c r="B22" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="24" t="n">
-        <v>13500000</v>
-      </c>
-      <c r="D22" s="24" t="n">
-        <v>17450000</v>
-      </c>
-      <c r="E22" s="24" t="n">
-        <v>-22300000</v>
-      </c>
-      <c r="F22" s="24" t="n">
-        <v>8650000</v>
-      </c>
-      <c r="G22" s="26" t="inlineStr">
-        <is>
-          <t>TIED TO SFP NOTE 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>FY 2024 — Land Held for Resale (IAS 2)</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="n">
-        <v>5400000</v>
-      </c>
-      <c r="C23" s="22" t="n">
-        <v>14600000</v>
-      </c>
-      <c r="D23" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="22" t="n">
-        <v>-11800000</v>
-      </c>
-      <c r="F23" s="22" t="n">
-        <v>8200000</v>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>PASSED (NRV &gt; Cost)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>FY 2024 — Construction WIP (IAS 2)</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="n">
-        <v>3250000</v>
-      </c>
-      <c r="C24" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="21" t="n">
-        <v>28750000</v>
-      </c>
-      <c r="E24" s="21" t="n">
-        <v>-26400000</v>
-      </c>
-      <c r="F24" s="21" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>PASSED (NRV &gt; Cost)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="23" t="inlineStr">
-        <is>
-          <t>FY 2024 — TOTAL INVENTORIES</t>
-        </is>
-      </c>
-      <c r="B25" s="24" t="n">
-        <v>8650000</v>
-      </c>
-      <c r="C25" s="24" t="n">
-        <v>14600000</v>
-      </c>
-      <c r="D25" s="24" t="n">
-        <v>28750000</v>
-      </c>
-      <c r="E25" s="24" t="n">
-        <v>-38200000</v>
-      </c>
-      <c r="F25" s="24" t="n">
-        <v>13800000</v>
-      </c>
-      <c r="G25" s="26" t="inlineStr">
-        <is>
-          <t>TIED TO SFP NOTE 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>FY 2025 — Land Held for Resale (IAS 2)</t>
-        </is>
-      </c>
-      <c r="B26" s="21" t="n">
-        <v>8200000</v>
-      </c>
-      <c r="C26" s="21" t="n">
-        <v>27700000</v>
-      </c>
-      <c r="D26" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="21" t="n">
-        <v>-21400000</v>
-      </c>
-      <c r="F26" s="21" t="n">
-        <v>14500000</v>
-      </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>PASSED (NRV &gt; Cost)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>FY 2025 — Construction WIP (IAS 2)</t>
-        </is>
-      </c>
-      <c r="B27" s="22" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="C27" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="22" t="n">
-        <v>49800000</v>
-      </c>
-      <c r="E27" s="22" t="n">
-        <v>-45600000</v>
-      </c>
-      <c r="F27" s="22" t="n">
-        <v>9800000</v>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>PASSED (NRV &gt; Cost)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="23" t="inlineStr">
-        <is>
-          <t>FY 2025 — TOTAL INVENTORIES</t>
-        </is>
-      </c>
-      <c r="B28" s="24" t="n">
-        <v>13800000</v>
-      </c>
-      <c r="C28" s="24" t="n">
-        <v>27700000</v>
-      </c>
-      <c r="D28" s="24" t="n">
-        <v>49800000</v>
-      </c>
-      <c r="E28" s="24" t="n">
-        <v>-67000000</v>
-      </c>
-      <c r="F28" s="24" t="n">
-        <v>24300000</v>
-      </c>
-      <c r="G28" s="26" t="inlineStr">
-        <is>
-          <t>TIED TO SFP NOTE 8</t>
-        </is>
-      </c>
+      <c r="G17" s="38" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12679,31 +12688,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="93" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="90" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BAAY PROJECTS LIMITED — PROPERTY, PLANT AND EQUIPMENT SCHEDULE (IAS 16)</t>
+          <t>BAAY PROJECTS LIMITED — PROPERTY, PLANT AND EQUIPMENT (IAS 16)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Fixed Asset Movement, Additions, Straight-Line Depreciation &amp; Net Book Value (2022 - 2025)</t>
+          <t>Schedule of Fixed Assets, Additions, Disposals &amp; Accumulated Depreciation (2023 - 2025)</t>
         </is>
       </c>
     </row>
@@ -12716,483 +12725,302 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Depr Rate (%)</t>
+          <t>Depr Method &amp; Rate</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Cost at 31 Dec 2022 (NGN)</t>
+          <t>Cost 31-Dec-2022</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2023 Additions (NGN)</t>
+          <t>2023 Additions</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Cost at 31 Dec 2023 (NGN)</t>
+          <t>Cost 31-Dec-2023</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2024 Additions (NGN)</t>
+          <t>2024 Additions</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Cost at 31 Dec 2024 (NGN)</t>
+          <t>Cost 31-Dec-2024</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>2025 Additions (NGN)</t>
+          <t>2025 Additions</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Cost at 31 Dec 2025 (NGN)</t>
+          <t>Cost 31-Dec-2025</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Office &amp; Site Equipment</t>
-        </is>
-      </c>
-      <c r="B5" s="35" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C5" s="22" t="n">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Plant, Machinery &amp; Site Equipment</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Straight Line 20%</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="n">
         <v>23850</v>
       </c>
-      <c r="D5" s="22" t="n">
+      <c r="D5" s="28" t="n">
         <v>1800000</v>
       </c>
-      <c r="E5" s="22" t="n">
+      <c r="E5" s="28" t="n">
         <v>1823850</v>
       </c>
-      <c r="F5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="22" t="n">
-        <v>1823850</v>
-      </c>
-      <c r="H5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="22" t="n">
-        <v>1823850</v>
+      <c r="F5" s="28" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>3023850</v>
+      </c>
+      <c r="H5" s="28" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="I5" s="28" t="n">
+        <v>4623850</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Motor &amp; Project Vehicles</t>
-        </is>
-      </c>
-      <c r="B6" s="36" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C6" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="21" t="n">
-        <v>2700000</v>
-      </c>
-      <c r="G6" s="21" t="n">
-        <v>2700000</v>
-      </c>
-      <c r="H6" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="21" t="n">
-        <v>2700000</v>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Motor Vehicles &amp; Logistics Fleet</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Straight Line 25%</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I6" s="27" t="n">
+        <v>3500000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Plant &amp; Heavy Construction Machinery</t>
-        </is>
-      </c>
-      <c r="B7" s="35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="22" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="I7" s="22" t="n">
-        <v>3600000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>TOTAL GROSS PPE COST</t>
-        </is>
-      </c>
-      <c r="B8" s="37" t="inlineStr"/>
-      <c r="C8" s="24">
-        <f>SUM(C5:C7)</f>
+      <c r="A7" s="39" t="inlineStr">
+        <is>
+          <t>TOTAL PPE GROSS COST</t>
+        </is>
+      </c>
+      <c r="B7" s="38" t="n"/>
+      <c r="C7" s="41">
+        <f>SUM(C5:C6)</f>
         <v/>
       </c>
-      <c r="D8" s="24">
-        <f>SUM(D5:D7)</f>
+      <c r="D7" s="41">
+        <f>SUM(D5:D6)</f>
         <v/>
       </c>
-      <c r="E8" s="24">
-        <f>SUM(E5:E7)</f>
+      <c r="E7" s="41">
+        <f>SUM(E5:E6)</f>
         <v/>
       </c>
-      <c r="F8" s="24">
-        <f>SUM(F5:F7)</f>
+      <c r="F7" s="41">
+        <f>SUM(F5:F6)</f>
         <v/>
       </c>
-      <c r="G8" s="24">
-        <f>SUM(G5:G7)</f>
+      <c r="G7" s="41">
+        <f>SUM(G5:G6)</f>
         <v/>
       </c>
-      <c r="H8" s="24">
-        <f>SUM(H5:H7)</f>
+      <c r="H7" s="41">
+        <f>SUM(H5:H6)</f>
         <v/>
       </c>
-      <c r="I8" s="24">
-        <f>SUM(I5:I7)</f>
+      <c r="I7" s="41">
+        <f>SUM(I5:I6)</f>
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9"/>
-    <row r="10"/>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ACCUMULATED DEPRECIATION &amp; NET BOOK VALUE ROLL-FORWARD</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>ACCUMULATED DEPRECIATION (IAS 16)</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Asset Category</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Accum Depr 2022</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>2023 Depr</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Accum Depr 2023</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>2024 Depr</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Accum Depr 2024</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>2025 Depr</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Accum Depr 2025</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>NBV 31-Dec-2025</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Asset Category</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Acc Dep 31 Dec 2022 (NGN)</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>2023 Charge (NGN)</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Acc Dep 31 Dec 2023 (NGN)</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>2024 Charge (NGN)</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Acc Dep 31 Dec 2024 (NGN)</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>2025 Charge (NGN)</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Acc Dep 31 Dec 2025 (NGN)</t>
-        </is>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Plant, Machinery &amp; Site Equipment</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="n">
+        <v>14310</v>
+      </c>
+      <c r="C12" s="27" t="n">
+        <v>385000</v>
+      </c>
+      <c r="D12" s="27" t="n">
+        <v>399310</v>
+      </c>
+      <c r="E12" s="27" t="n">
+        <v>485000</v>
+      </c>
+      <c r="F12" s="27" t="n">
+        <v>884310</v>
+      </c>
+      <c r="G12" s="27" t="n">
+        <v>785000</v>
+      </c>
+      <c r="H12" s="27" t="n">
+        <v>1669310</v>
+      </c>
+      <c r="I12" s="27" t="n">
+        <v>2954540</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Office &amp; Site Equipment</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="n">
-        <v>14310</v>
-      </c>
-      <c r="C13" s="22" t="n">
-        <v>385000</v>
-      </c>
-      <c r="D13" s="22" t="n">
-        <v>399310</v>
-      </c>
-      <c r="E13" s="22" t="n">
-        <v>377500</v>
-      </c>
-      <c r="F13" s="22" t="n">
-        <v>776810</v>
-      </c>
-      <c r="G13" s="22" t="n">
-        <v>247500</v>
-      </c>
-      <c r="H13" s="22" t="n">
-        <v>1024310</v>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Motor Vehicles &amp; Logistics Fleet</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="F13" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="G13" s="28" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H13" s="28" t="n">
+        <v>730000</v>
+      </c>
+      <c r="I13" s="28" t="n">
+        <v>2770000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Motor &amp; Project Vehicles</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="21" t="n">
-        <v>337500</v>
-      </c>
-      <c r="F14" s="21" t="n">
-        <v>337500</v>
-      </c>
-      <c r="G14" s="21" t="n">
-        <v>675000</v>
-      </c>
-      <c r="H14" s="21" t="n">
-        <v>1012500</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Plant &amp; Heavy Construction Machinery</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="22" t="n">
-        <v>362500</v>
-      </c>
-      <c r="H15" s="22" t="n">
-        <v>362500</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="23" t="inlineStr">
-        <is>
-          <t>TOTAL ACCUMULATED DEPRECIATION</t>
-        </is>
-      </c>
-      <c r="B16" s="24">
-        <f>SUM(B13:B15)</f>
+      <c r="A14" s="39" t="inlineStr">
+        <is>
+          <t>TOTAL ACCUMULATED DEPRECIATION / NBV</t>
+        </is>
+      </c>
+      <c r="B14" s="41">
+        <f>SUM(B12:B13)</f>
         <v/>
       </c>
-      <c r="C16" s="24">
-        <f>SUM(C13:C15)</f>
+      <c r="C14" s="41">
+        <f>SUM(C12:C13)</f>
         <v/>
       </c>
-      <c r="D16" s="24">
-        <f>SUM(D13:D15)</f>
+      <c r="D14" s="41">
+        <f>SUM(D12:D13)</f>
         <v/>
       </c>
-      <c r="E16" s="24">
-        <f>SUM(E13:E15)</f>
+      <c r="E14" s="41">
+        <f>SUM(E12:E13)</f>
         <v/>
       </c>
-      <c r="F16" s="24">
-        <f>SUM(F13:F15)</f>
+      <c r="F14" s="41">
+        <f>SUM(F12:F13)</f>
         <v/>
       </c>
-      <c r="G16" s="24">
-        <f>SUM(G13:G15)</f>
+      <c r="G14" s="41">
+        <f>SUM(G12:G13)</f>
         <v/>
       </c>
-      <c r="H16" s="24">
-        <f>SUM(H13:H15)</f>
+      <c r="H14" s="41">
+        <f>SUM(H12:H13)</f>
         <v/>
       </c>
-    </row>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>NET BOOK VALUE (CARRYING AMOUNT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Asset Category</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>31 Dec 2022 (NGN)</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>31 Dec 2023 (NGN)</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>31 Dec 2024 (NGN)</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>31 Dec 2025 (NGN)</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>IAS 16 Compliance Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Office &amp; Site Equipment</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="n">
-        <v>9540</v>
-      </c>
-      <c r="C21" s="22" t="n">
-        <v>1424540</v>
-      </c>
-      <c r="D21" s="22" t="n">
-        <v>1047040</v>
-      </c>
-      <c r="E21" s="22" t="n">
-        <v>799540</v>
-      </c>
-      <c r="F21" s="38" t="inlineStr">
-        <is>
-          <t>Depreciated at 25% Straight-Line</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Motor &amp; Project Vehicles</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="21" t="n">
-        <v>2362500</v>
-      </c>
-      <c r="E22" s="21" t="n">
-        <v>1687500</v>
-      </c>
-      <c r="F22" s="39" t="inlineStr">
-        <is>
-          <t>Depreciated at 25% Straight-Line</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>Plant &amp; Heavy Construction Machinery</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="22" t="n">
-        <v>3237500</v>
-      </c>
-      <c r="F23" s="38" t="inlineStr">
-        <is>
-          <t>Depreciated at 20% Straight-Line</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="23" t="inlineStr">
-        <is>
-          <t>TOTAL PPE NET BOOK VALUE</t>
-        </is>
-      </c>
-      <c r="B24" s="24">
-        <f>SUM(B21:B23)</f>
+      <c r="I14" s="41">
+        <f>SUM(I12:I13)</f>
         <v/>
-      </c>
-      <c r="C24" s="24">
-        <f>SUM(C21:C23)</f>
-        <v/>
-      </c>
-      <c r="D24" s="24">
-        <f>SUM(D21:D23)</f>
-        <v/>
-      </c>
-      <c r="E24" s="24">
-        <f>SUM(E21:E23)</f>
-        <v/>
-      </c>
-      <c r="F24" s="26" t="inlineStr">
-        <is>
-          <t>TIED TO SFP NOTE 7</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -13206,31 +13034,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="47" customWidth="1" min="7" max="7"/>
-    <col width="33" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="103" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BAAY PROJECTS LIMITED — RECEIVABLES, ECL (IFRS 9) &amp; PAYABLES SUBLEDGER</t>
+          <t>BAAY PROJECTS LIMITED — RECEIVABLES, IFRS 9 ECL &amp; TRADE PAYABLES</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Aging Analysis, IFRS 9 Expected Credit Loss Matrix &amp; Trade Payables Subledger</t>
+          <t>Aging Analysis, Simplified ECL Matrix, Customer Subscriptions &amp; Subcontractor Payables (2023 - 2025)</t>
         </is>
       </c>
     </row>
@@ -13238,403 +13066,239 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Debtor / Customer Account</t>
+          <t>Aging Category</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Current (0-30 days)</t>
+          <t>Gross Balance 2023</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>31-60 days</t>
+          <t>ECL Rate (%)</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>61-90 days</t>
+          <t>2023 ECL (NGN)</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Over 90 days</t>
+          <t>Gross Balance 2024</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Gross Carrying Amount (NGN)</t>
+          <t>2024 ECL (NGN)</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>ECL Loss Rate (%)</t>
+          <t>Gross Balance 2025</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>ECL Impairment Allowance (NGN)</t>
+          <t>2025 ECL (NGN)</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Net Carrying Amount (NGN)</t>
+          <t>Net Balance 2025 (NGN)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Apex Properties Ltd (Lekki Phase 1)</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="C5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="22" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="G5" s="35" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H5" s="22" t="n">
-        <v>50000</v>
-      </c>
-      <c r="I5" s="22" t="n">
-        <v>2450000</v>
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>0 - 30 Days (Current)</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="n">
+        <v>2150000</v>
+      </c>
+      <c r="C5" s="33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D5" s="28" t="n">
+        <v>21500</v>
+      </c>
+      <c r="E5" s="28" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="F5" s="28" t="n">
+        <v>34000</v>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="H5" s="28" t="n">
+        <v>52000</v>
+      </c>
+      <c r="I5" s="28" t="n">
+        <v>5148000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Horizon Holdings Ltd (Ikeja Commercial)</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="21" t="n">
-        <v>650000</v>
-      </c>
-      <c r="D6" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="21" t="n">
-        <v>650000</v>
-      </c>
-      <c r="G6" s="36" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H6" s="21" t="n">
-        <v>32500</v>
-      </c>
-      <c r="I6" s="21" t="n">
-        <v>617500</v>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>31 - 90 Days (Past Due)</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="n">
+        <v>950000</v>
+      </c>
+      <c r="C6" s="36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D6" s="27" t="n">
+        <v>28500</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>1450000</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>43500</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>69000</v>
+      </c>
+      <c r="I6" s="27" t="n">
+        <v>2231000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Private Land Buyers (Ibeju Scheme 1)</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="22" t="n">
-        <v>500000</v>
-      </c>
-      <c r="E7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="22" t="n">
-        <v>500000</v>
-      </c>
-      <c r="G7" s="35" t="n">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>91 - 180 Days (Past Due)</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="n">
+        <v>350000</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>24500</v>
+      </c>
+      <c r="E7" s="28" t="n">
+        <v>550000</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>38500</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>950000</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>66500</v>
+      </c>
+      <c r="I7" s="28" t="n">
+        <v>883500</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>181 - 360 Days (Past Due)</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="n">
+        <v>120000</v>
+      </c>
+      <c r="C8" s="36" t="n">
         <v>0.15</v>
       </c>
-      <c r="H7" s="22" t="n">
+      <c r="D8" s="27" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>250000</v>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>37500</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>450000</v>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>67500</v>
+      </c>
+      <c r="I8" s="27" t="n">
+        <v>382500</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>&gt; 360 Days (Impaired)</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="n">
+        <v>80000</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E9" s="28" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>37500</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>300000</v>
+      </c>
+      <c r="H9" s="28" t="n">
         <v>75000</v>
       </c>
-      <c r="I7" s="22" t="n">
-        <v>425000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Historical 2022 Contract Retentions</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="36" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H8" s="21" t="n">
-        <v>27500</v>
-      </c>
-      <c r="I8" s="21" t="n">
-        <v>-27500</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="23" t="inlineStr">
-        <is>
-          <t>TOTAL TRADE RECEIVABLES 2023</t>
-        </is>
-      </c>
-      <c r="B9" s="24">
-        <f>SUM(B5:B8)</f>
+      <c r="I9" s="28" t="n">
+        <v>225000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="39" t="inlineStr">
+        <is>
+          <t>TOTAL TRADE RECEIVABLES &amp; ECL</t>
+        </is>
+      </c>
+      <c r="B10" s="41">
+        <f>SUM(B5:B9)</f>
         <v/>
       </c>
-      <c r="C9" s="24">
-        <f>SUM(C5:C8)</f>
+      <c r="C10" s="38" t="n"/>
+      <c r="D10" s="41">
+        <f>SUM(D5:D9)</f>
         <v/>
       </c>
-      <c r="D9" s="24">
-        <f>SUM(D5:D8)</f>
+      <c r="E10" s="41">
+        <f>SUM(E5:E9)</f>
         <v/>
       </c>
-      <c r="E9" s="24">
-        <f>SUM(E5:E8)</f>
+      <c r="F10" s="41">
+        <f>SUM(F5:F9)</f>
         <v/>
       </c>
-      <c r="F9" s="24">
-        <f>SUM(F5:F8)</f>
+      <c r="G10" s="41">
+        <f>SUM(G5:G9)</f>
         <v/>
       </c>
-      <c r="G9" s="37" t="inlineStr"/>
-      <c r="H9" s="24">
-        <f>SUM(H5:H8)</f>
+      <c r="H10" s="41">
+        <f>SUM(H5:H9)</f>
         <v/>
       </c>
-      <c r="I9" s="24">
-        <f>F9-H9</f>
+      <c r="I10" s="41">
+        <f>SUM(I5:I9)</f>
         <v/>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRADE AND OTHER PAYABLES SUBLEDGER (2022 - 2025)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Creditor / Supplier / Accrual Account</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>31 Dec 2022 (NGN)</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>31 Dec 2023 (NGN)</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>31 Dec 2024 (NGN)</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>31 Dec 2025 (NGN)</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>Payment Terms &amp; Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Titan Piling Nig Ltd (Subcontractor)</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Trade Subcontractor</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="21" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="E14" s="21" t="n">
-        <v>2100000</v>
-      </c>
-      <c r="F14" s="21" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="G14" s="40" t="inlineStr">
-        <is>
-          <t>30-day certificate settlement terms</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Prime Steel &amp; Cement Ltd (Materials)</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Direct Material Supplier</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="n">
-        <v>25000</v>
-      </c>
-      <c r="D15" s="22" t="n">
-        <v>950000</v>
-      </c>
-      <c r="E15" s="22" t="n">
-        <v>1750000</v>
-      </c>
-      <c r="F15" s="22" t="n">
-        <v>3050000</v>
-      </c>
-      <c r="G15" s="41" t="inlineStr">
-        <is>
-          <t>Commercial invoice credit facility</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>PKF &amp; Co. / Baker &amp; Associates (Audit Fees)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Audit Fee Accrual</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D16" s="21" t="n">
-        <v>375000</v>
-      </c>
-      <c r="E16" s="21" t="n">
-        <v>550000</v>
-      </c>
-      <c r="F16" s="21" t="n">
-        <v>850000</v>
-      </c>
-      <c r="G16" s="40" t="inlineStr">
-        <is>
-          <t>Statutory audit fee accrued annually</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Sundry Site Operating &amp; Utilities Accruals</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Operational Accruals</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="22" t="n">
-        <v>245235</v>
-      </c>
-      <c r="E17" s="22" t="n">
-        <v>425500</v>
-      </c>
-      <c r="F17" s="22" t="n">
-        <v>683500</v>
-      </c>
-      <c r="G17" s="41" t="inlineStr">
-        <is>
-          <t>Electricity, communication and site security</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="inlineStr">
-        <is>
-          <t>TOTAL TRADE AND OTHER PAYABLES</t>
-        </is>
-      </c>
-      <c r="B18" s="34" t="inlineStr">
-        <is>
-          <t>Current Liabilities</t>
-        </is>
-      </c>
-      <c r="C18" s="24">
-        <f>SUM(C14:C17)</f>
-        <v/>
-      </c>
-      <c r="D18" s="24">
-        <f>SUM(D14:D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="24">
-        <f>SUM(E14:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="24">
-        <f>SUM(F14:F17)</f>
-        <v/>
-      </c>
-      <c r="G18" s="26" t="inlineStr">
-        <is>
-          <t>TIED TO SFP NOTE 14</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -13648,16 +13312,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="84" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="109" customWidth="1" min="7" max="7"/>
+    <col width="97" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13670,7 +13334,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Director Current Accounts, Trade Alias Movements &amp; Statement of Changes in Equity</t>
+          <t>Director Financing, Key Management Compensation &amp; Statement of Changes in Equity (2022 - 2025)</t>
         </is>
       </c>
     </row>
@@ -13678,382 +13342,407 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Related Party / Entity Name</t>
+          <t>Transaction / Entity Line</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Relationship &amp; Nature</t>
+          <t>Related Party Name &amp; Designation</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>31 Dec 2022 (NGN)</t>
+          <t>Relationship Basis</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>31 Dec 2023 (NGN)</t>
+          <t>2022 (NGN)</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>31 Dec 2024 (NGN)</t>
+          <t>2023 (NGN)</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>31 Dec 2025 (NGN)</t>
+          <t>2024 (NGN)</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Terms, Interest &amp; Subordination Status</t>
+          <t>2025 (NGN)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Director Financing Loan (Opening)</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Engr. Babatunde Goke</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Managing Director / Controlling Shareholder</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="22" t="n">
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Managing Director / 70% Shareholder</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="28" t="n">
         <v>4500000</v>
       </c>
-      <c r="E5" s="22" t="n">
+      <c r="G5" s="28" t="n">
         <v>5800000</v>
       </c>
-      <c r="F5" s="22" t="n">
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>New Direct Advances Injected</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Engr. Babatunde Goke</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Project Liquidity Support</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>1700000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Repayments to Director</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Engr. Babatunde Goke</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Cash Reimbursement</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Director Project Loan (Closing SFP)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Engr. Babatunde Goke</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Unsecured, Interest-Free, Subordinated</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="G8" s="27" t="n">
         <v>7500000</v>
       </c>
-      <c r="G5" s="41" t="inlineStr">
-        <is>
-          <t>Unsecured, non-interest bearing long-term project funding facility; subordinated to third-party bank debt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Baay Gokes (Business Name Alias)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Trade Alias (Same Legal Entity RC 1526224)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="40" t="inlineStr">
-        <is>
-          <t>All bank accounts &amp; transactions merged into Baay Projects Limited. Zero intercompany balance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Baay Degok (Business Name Alias)</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Trade Alias (Same Legal Entity RC 1526224)</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="41" t="inlineStr">
-        <is>
-          <t>All bank accounts &amp; transactions merged into Baay Projects Limited. Zero intercompany balance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>TOTAL RELATED PARTY BORROWINGS</t>
-        </is>
-      </c>
-      <c r="B8" s="34" t="inlineStr">
-        <is>
-          <t>Non-Current Liabilities</t>
-        </is>
-      </c>
-      <c r="C8" s="24">
-        <f>SUM(C5:C7)</f>
-        <v/>
-      </c>
-      <c r="D8" s="24">
-        <f>SUM(D5:D7)</f>
-        <v/>
-      </c>
-      <c r="E8" s="24">
-        <f>SUM(E5:E7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="24">
-        <f>SUM(F5:F7)</f>
-        <v/>
-      </c>
-      <c r="G8" s="26" t="inlineStr">
-        <is>
-          <t>TIED TO SFP NOTE 17</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Executive Directors' Remuneration</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Engr. &amp; Mrs. Goke</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Key Management Personnel</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="28" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>3600000</v>
+      </c>
+    </row>
     <row r="10"/>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>STATEMENT OF CHANGES IN EQUITY (2022 - 2025)</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>STATEMENT OF CHANGES IN EQUITY ROLL-FORWARD (2022 - 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Equity Component</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Ordinary Share Capital (NGN)</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Share Capital (NGN)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Retained Earnings (NGN)</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Total Shareholders' Equity (NGN)</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Audit Movement Verification</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Balance at 1 January 2022</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="n">
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Total Equity (NGN)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Statutory Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 1 January 2022</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="n">
         <v>1000000</v>
       </c>
-      <c r="C13" s="22" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="D13" s="22" t="n">
-        <v>2650000</v>
-      </c>
-      <c r="E13" s="38" t="inlineStr">
-        <is>
-          <t>Opening Share Capital &amp; Earnings</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Profit for the Year 2022</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="21" t="n">
-        <v>711708</v>
-      </c>
-      <c r="D14" s="21" t="n">
-        <v>711708</v>
-      </c>
-      <c r="E14" s="39" t="inlineStr">
-        <is>
-          <t>2022 Audited AFS Net Profit</t>
+      <c r="C14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Incorporation &amp; Opening</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>Balance at 31 December 2022</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="n">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Profit for the Year 2022 (Audited)</t>
+        </is>
+      </c>
+      <c r="B15" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="28" t="n">
+        <v>2361708</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>2361708</v>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>2022 Audited AFS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2022</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="n">
         <v>1000000</v>
       </c>
-      <c r="C15" s="24" t="n">
+      <c r="C16" s="27" t="n">
         <v>2361708</v>
       </c>
-      <c r="D15" s="24" t="n">
+      <c r="D16" s="19" t="n">
         <v>3361708</v>
       </c>
-      <c r="E15" s="26" t="inlineStr">
-        <is>
-          <t>Audited 2022 Balance Sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Profit for the Year 2023</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="21" t="n">
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Audited Balance Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Profit for the Year 2023 (Draft AFS)</t>
+        </is>
+      </c>
+      <c r="B17" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="28" t="n">
         <v>5600235</v>
       </c>
-      <c r="D16" s="21" t="n">
+      <c r="D17" s="17" t="n">
         <v>5600235</v>
       </c>
-      <c r="E16" s="39" t="inlineStr">
-        <is>
-          <t>Statement of Profit or Loss FY 2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="23" t="inlineStr">
-        <is>
-          <t>Balance at 31 December 2023</t>
-        </is>
-      </c>
-      <c r="B17" s="24" t="n">
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Statement of Profit or Loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2023</t>
+        </is>
+      </c>
+      <c r="B18" s="27" t="n">
         <v>1000000</v>
       </c>
-      <c r="C17" s="24" t="n">
+      <c r="C18" s="27" t="n">
         <v>7961943</v>
       </c>
-      <c r="D17" s="24" t="n">
+      <c r="D18" s="19" t="n">
         <v>8961943</v>
       </c>
-      <c r="E17" s="26" t="inlineStr">
-        <is>
-          <t>Audited SFP 31 Dec 2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Profit for the Year 2024</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="21" t="n">
-        <v>9514775</v>
-      </c>
-      <c r="D18" s="21" t="n">
-        <v>9514775</v>
-      </c>
-      <c r="E18" s="39" t="inlineStr">
-        <is>
-          <t>Statement of Profit or Loss FY 2024</t>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Statement of Financial Position</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="inlineStr">
-        <is>
-          <t>Balance at 31 December 2024</t>
-        </is>
-      </c>
-      <c r="B19" s="24" t="n">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Profit for the Year 2024 (Draft AFS)</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="28" t="n">
+        <v>5514775</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>5514775</v>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Statement of Profit or Loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2024</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="n">
         <v>1000000</v>
       </c>
-      <c r="C19" s="24" t="n">
-        <v>17476718</v>
-      </c>
-      <c r="D19" s="24" t="n">
-        <v>18476718</v>
-      </c>
-      <c r="E19" s="26" t="inlineStr">
-        <is>
-          <t>Audited SFP 31 Dec 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Profit for the Year 2025</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="21" t="n">
-        <v>14899870</v>
-      </c>
-      <c r="D20" s="21" t="n">
-        <v>14899870</v>
-      </c>
-      <c r="E20" s="39" t="inlineStr">
-        <is>
-          <t>Statement of Profit or Loss FY 2025</t>
+      <c r="C20" s="27" t="n">
+        <v>13476718</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>14476718</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Statement of Financial Position</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="inlineStr">
-        <is>
-          <t>Balance at 31 December 2025</t>
-        </is>
-      </c>
-      <c r="B21" s="24" t="n">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Profit for the Year 2025 (Draft AFS)</t>
+        </is>
+      </c>
+      <c r="B21" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="28" t="n">
+        <v>8802370</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>8802370</v>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>Statement of Profit or Loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2025</t>
+        </is>
+      </c>
+      <c r="B22" s="27" t="n">
         <v>1000000</v>
       </c>
-      <c r="C21" s="24" t="n">
-        <v>32376588</v>
-      </c>
-      <c r="D21" s="24" t="n">
-        <v>33376588</v>
-      </c>
-      <c r="E21" s="26" t="inlineStr">
-        <is>
-          <t>Audited SFP 31 Dec 2025</t>
+      <c r="C22" s="27" t="n">
+        <v>22279088</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>23279088</v>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Statement of Financial Position</t>
         </is>
       </c>
     </row>
@@ -15418,7 +15107,7 @@
       <c r="E13" s="24" t="n">
         <v>24500000</v>
       </c>
-      <c r="F13" s="34" t="inlineStr">
+      <c r="F13" s="42" t="inlineStr">
         <is>
           <t>TETFA 2011 Sec 1(2)</t>
         </is>
@@ -15469,7 +15158,7 @@
       <c r="E15" s="24" t="n">
         <v>22750000</v>
       </c>
-      <c r="F15" s="34" t="inlineStr">
+      <c r="F15" s="42" t="inlineStr">
         <is>
           <t>CITA Section 40</t>
         </is>
@@ -15486,13 +15175,13 @@
           <t>Statutory Rate</t>
         </is>
       </c>
-      <c r="C16" s="42" t="n">
+      <c r="C16" s="43" t="n">
         <v>0.2</v>
       </c>
-      <c r="D16" s="42" t="n">
+      <c r="D16" s="43" t="n">
         <v>0.2</v>
       </c>
-      <c r="E16" s="42" t="n">
+      <c r="E16" s="43" t="n">
         <v>0.3</v>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -15537,13 +15226,13 @@
           <t>Finance Act 2023 Rate</t>
         </is>
       </c>
-      <c r="C18" s="42" t="n">
+      <c r="C18" s="43" t="n">
         <v>0.03</v>
       </c>
-      <c r="D18" s="42" t="n">
+      <c r="D18" s="43" t="n">
         <v>0.03</v>
       </c>
-      <c r="E18" s="42" t="n">
+      <c r="E18" s="43" t="n">
         <v>0.03</v>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -15706,7 +15395,7 @@
       <c r="E24" s="24" t="n">
         <v>7617630</v>
       </c>
-      <c r="F24" s="34" t="inlineStr">
+      <c r="F24" s="42" t="inlineStr">
         <is>
           <t>TIED TO NOTE 16</t>
         </is>
@@ -15805,10 +15494,10 @@
           <t>FY 2023 — Office &amp; Site Equipment</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n">
+      <c r="B5" s="44" t="n">
         <v>0.5</v>
       </c>
-      <c r="C5" s="35" t="n">
+      <c r="C5" s="44" t="n">
         <v>0.25</v>
       </c>
       <c r="D5" s="22" t="n">
@@ -15836,8 +15525,8 @@
           <t>FY 2023 — TOTAL CAPITAL ALLOWANCE CLAIMED</t>
         </is>
       </c>
-      <c r="B6" s="37" t="inlineStr"/>
-      <c r="C6" s="37" t="inlineStr"/>
+      <c r="B6" s="45" t="inlineStr"/>
+      <c r="C6" s="45" t="inlineStr"/>
       <c r="D6" s="24" t="n">
         <v>9540</v>
       </c>
@@ -15863,10 +15552,10 @@
           <t>FY 2024 — Office &amp; Site Equipment</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="44" t="n">
         <v>0.5</v>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="44" t="n">
         <v>0.25</v>
       </c>
       <c r="D7" s="22" t="n">
@@ -15894,10 +15583,10 @@
           <t>FY 2024 — Motor &amp; Project Vehicles</t>
         </is>
       </c>
-      <c r="B8" s="36" t="n">
+      <c r="B8" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="C8" s="36" t="n">
+      <c r="C8" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="D8" s="21" t="n">
@@ -15925,8 +15614,8 @@
           <t>FY 2024 — TOTAL CAPITAL ALLOWANCE CLAIMED</t>
         </is>
       </c>
-      <c r="B9" s="37" t="inlineStr"/>
-      <c r="C9" s="37" t="inlineStr"/>
+      <c r="B9" s="45" t="inlineStr"/>
+      <c r="C9" s="45" t="inlineStr"/>
       <c r="D9" s="24" t="n">
         <v>1289540</v>
       </c>
@@ -15952,10 +15641,10 @@
           <t>FY 2025 — Office &amp; Site Equipment</t>
         </is>
       </c>
-      <c r="B10" s="36" t="n">
+      <c r="B10" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="C10" s="36" t="n">
+      <c r="C10" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="D10" s="21" t="n">
@@ -15983,10 +15672,10 @@
           <t>FY 2025 — Motor &amp; Project Vehicles</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="44" t="n">
         <v>0.5</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="44" t="n">
         <v>0.25</v>
       </c>
       <c r="D11" s="22" t="n">
@@ -16014,10 +15703,10 @@
           <t>FY 2025 — Plant &amp; Heavy Machinery</t>
         </is>
       </c>
-      <c r="B12" s="36" t="n">
+      <c r="B12" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="C12" s="36" t="n">
+      <c r="C12" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="D12" s="21" t="n">
@@ -16045,8 +15734,8 @@
           <t>FY 2025 — TOTAL CAPITAL ALLOWANCE CLAIMED</t>
         </is>
       </c>
-      <c r="B13" s="37" t="inlineStr"/>
-      <c r="C13" s="37" t="inlineStr"/>
+      <c r="B13" s="45" t="inlineStr"/>
+      <c r="C13" s="45" t="inlineStr"/>
       <c r="D13" s="24" t="n">
         <v>3009540</v>
       </c>
@@ -16638,7 +16327,7 @@
       <c r="C5" s="22" t="n">
         <v>22000000</v>
       </c>
-      <c r="D5" s="35" t="n">
+      <c r="D5" s="44" t="n">
         <v>0.05</v>
       </c>
       <c r="E5" s="22" t="n">
@@ -16670,7 +16359,7 @@
       <c r="C6" s="21" t="n">
         <v>4000000</v>
       </c>
-      <c r="D6" s="36" t="n">
+      <c r="D6" s="46" t="n">
         <v>0.05</v>
       </c>
       <c r="E6" s="21" t="n">
@@ -16694,7 +16383,7 @@
           <t>TOTAL WHT RECEIVABLE 2023</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="42" t="inlineStr">
         <is>
           <t>Carried Forward as CIT Tax Credit</t>
         </is>
@@ -16703,12 +16392,12 @@
         <f>SUM(C5:C6)</f>
         <v/>
       </c>
-      <c r="D7" s="37" t="inlineStr"/>
+      <c r="D7" s="45" t="inlineStr"/>
       <c r="E7" s="24">
         <f>SUM(E5:E6)</f>
         <v/>
       </c>
-      <c r="F7" s="43" t="inlineStr">
+      <c r="F7" s="47" t="inlineStr">
         <is>
           <t>TIED TO SFP NOTE 10</t>
         </is>
@@ -16812,7 +16501,7 @@
       <c r="D5" s="22" t="n">
         <v>135000</v>
       </c>
-      <c r="E5" s="35" t="n">
+      <c r="E5" s="44" t="n">
         <v>0.2</v>
       </c>
       <c r="F5" s="22" t="n">
@@ -16837,7 +16526,7 @@
       <c r="D6" s="21" t="n">
         <v>-185000</v>
       </c>
-      <c r="E6" s="36" t="n">
+      <c r="E6" s="46" t="n">
         <v>0.2</v>
       </c>
       <c r="F6" s="21" t="n">
@@ -16862,7 +16551,7 @@
       <c r="D7" s="22" t="n">
         <v>-110000</v>
       </c>
-      <c r="E7" s="35" t="n">
+      <c r="E7" s="44" t="n">
         <v>0.2</v>
       </c>
       <c r="F7" s="22" t="n">
@@ -16890,7 +16579,7 @@
         <f>SUM(D5:D7)</f>
         <v/>
       </c>
-      <c r="E8" s="37" t="inlineStr"/>
+      <c r="E8" s="45" t="inlineStr"/>
       <c r="F8" s="24" t="n">
         <v>32000</v>
       </c>
@@ -16913,7 +16602,7 @@
       <c r="D9" s="22" t="n">
         <v>400000</v>
       </c>
-      <c r="E9" s="35" t="n">
+      <c r="E9" s="44" t="n">
         <v>0.2</v>
       </c>
       <c r="F9" s="22" t="n">
@@ -16938,7 +16627,7 @@
       <c r="D10" s="21" t="n">
         <v>-445000</v>
       </c>
-      <c r="E10" s="36" t="n">
+      <c r="E10" s="46" t="n">
         <v>0.2</v>
       </c>
       <c r="F10" s="21" t="n">
@@ -16963,7 +16652,7 @@
       <c r="D11" s="22" t="n">
         <v>-125000</v>
       </c>
-      <c r="E11" s="35" t="n">
+      <c r="E11" s="44" t="n">
         <v>0.2</v>
       </c>
       <c r="F11" s="22" t="n">
@@ -16991,7 +16680,7 @@
         <f>SUM(D9:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="37" t="inlineStr"/>
+      <c r="E12" s="45" t="inlineStr"/>
       <c r="F12" s="24" t="n">
         <v>-16000</v>
       </c>
@@ -17014,7 +16703,7 @@
       <c r="D13" s="22" t="n">
         <v>865000</v>
       </c>
-      <c r="E13" s="35" t="n">
+      <c r="E13" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F13" s="22" t="n">
@@ -17039,7 +16728,7 @@
       <c r="D14" s="21" t="n">
         <v>-840000</v>
       </c>
-      <c r="E14" s="36" t="n">
+      <c r="E14" s="46" t="n">
         <v>0.3</v>
       </c>
       <c r="F14" s="21" t="n">
@@ -17064,7 +16753,7 @@
       <c r="D15" s="22" t="n">
         <v>-303333.33</v>
       </c>
-      <c r="E15" s="35" t="n">
+      <c r="E15" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F15" s="22" t="n">
@@ -17092,7 +16781,7 @@
         <f>SUM(D13:D15)</f>
         <v/>
       </c>
-      <c r="E16" s="37" t="inlineStr"/>
+      <c r="E16" s="45" t="inlineStr"/>
       <c r="F16" s="24" t="n">
         <v>-98500</v>
       </c>
@@ -17205,7 +16894,7 @@
       <c r="G5" s="22" t="n">
         <v>1492000</v>
       </c>
-      <c r="H5" s="41" t="inlineStr">
+      <c r="H5" s="48" t="inlineStr">
         <is>
           <t>Assessed / Payable YOA 2024</t>
         </is>
@@ -17235,7 +16924,7 @@
       <c r="G6" s="21" t="n">
         <v>239400</v>
       </c>
-      <c r="H6" s="40" t="inlineStr">
+      <c r="H6" s="49" t="inlineStr">
         <is>
           <t>Assessed / Payable YOA 2024</t>
         </is>
@@ -17265,7 +16954,7 @@
       <c r="G7" s="22" t="n">
         <v>455</v>
       </c>
-      <c r="H7" s="41" t="inlineStr">
+      <c r="H7" s="48" t="inlineStr">
         <is>
           <t>Includes ₦90 opening arrears</t>
         </is>
@@ -17325,7 +17014,7 @@
       <c r="G9" s="22" t="n">
         <v>2128000</v>
       </c>
-      <c r="H9" s="41" t="inlineStr">
+      <c r="H9" s="48" t="inlineStr">
         <is>
           <t>2023 CIT Paid; WHT Credit Applied</t>
         </is>
@@ -17355,7 +17044,7 @@
       <c r="G10" s="21" t="n">
         <v>408600</v>
       </c>
-      <c r="H10" s="40" t="inlineStr">
+      <c r="H10" s="49" t="inlineStr">
         <is>
           <t>2023 TET Remitted</t>
         </is>
@@ -17385,7 +17074,7 @@
       <c r="G11" s="22" t="n">
         <v>625</v>
       </c>
-      <c r="H11" s="41" t="inlineStr">
+      <c r="H11" s="48" t="inlineStr">
         <is>
           <t>Opening PTF Arrears Settled</t>
         </is>
@@ -17445,7 +17134,7 @@
       <c r="G13" s="22" t="n">
         <v>4825000</v>
       </c>
-      <c r="H13" s="41" t="inlineStr">
+      <c r="H13" s="48" t="inlineStr">
         <is>
           <t>2024 CIT Paid; ₦2m WHT Utilized</t>
         </is>
@@ -17475,7 +17164,7 @@
       <c r="G14" s="21" t="n">
         <v>735000</v>
       </c>
-      <c r="H14" s="40" t="inlineStr">
+      <c r="H14" s="49" t="inlineStr">
         <is>
           <t>2024 TET Remitted</t>
         </is>
@@ -17505,7 +17194,7 @@
       <c r="G15" s="22" t="n">
         <v>1130</v>
       </c>
-      <c r="H15" s="41" t="inlineStr">
+      <c r="H15" s="48" t="inlineStr">
         <is>
           <t>2024 PTF Remitted</t>
         </is>
@@ -17535,7 +17224,7 @@
       <c r="G16" s="21" t="n">
         <v>56500</v>
       </c>
-      <c r="H16" s="40" t="inlineStr">
+      <c r="H16" s="49" t="inlineStr">
         <is>
           <t>0.25% Large Company Levy</t>
         </is>
@@ -17654,10 +17343,10 @@
           <t>NON-CURRENT ASSETS</t>
         </is>
       </c>
-      <c r="B7" s="44" t="n"/>
-      <c r="C7" s="44" t="n"/>
-      <c r="D7" s="44" t="n"/>
-      <c r="E7" s="44" t="n"/>
+      <c r="B7" s="50" t="n"/>
+      <c r="C7" s="50" t="n"/>
+      <c r="D7" s="50" t="n"/>
+      <c r="E7" s="50" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -17676,7 +17365,7 @@
       <c r="D8" s="21" t="n">
         <v>9540</v>
       </c>
-      <c r="E8" s="40" t="inlineStr">
+      <c r="E8" s="49" t="inlineStr">
         <is>
           <t>IAS 16 Carrying Amount</t>
         </is>
@@ -17699,28 +17388,28 @@
       <c r="D9" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="40" t="inlineStr">
+      <c r="E9" s="49" t="inlineStr">
         <is>
           <t>IAS 12 Temporary Differences</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="45" t="inlineStr">
+      <c r="A10" s="51" t="inlineStr">
         <is>
           <t>TOTAL NON-CURRENT ASSETS</t>
         </is>
       </c>
-      <c r="B10" s="46" t="n"/>
-      <c r="C10" s="47">
+      <c r="B10" s="52" t="n"/>
+      <c r="C10" s="53">
         <f>SUM(C8:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="47">
+      <c r="D10" s="53">
         <f>SUM(D8:D9)</f>
         <v/>
       </c>
-      <c r="E10" s="48" t="inlineStr">
+      <c r="E10" s="54" t="inlineStr">
         <is>
           <t>TIED OUT</t>
         </is>
@@ -17732,10 +17421,10 @@
           <t>CURRENT ASSETS</t>
         </is>
       </c>
-      <c r="B11" s="44" t="n"/>
-      <c r="C11" s="44" t="n"/>
-      <c r="D11" s="44" t="n"/>
-      <c r="E11" s="44" t="n"/>
+      <c r="B11" s="50" t="n"/>
+      <c r="C11" s="50" t="n"/>
+      <c r="D11" s="50" t="n"/>
+      <c r="E11" s="50" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -17754,7 +17443,7 @@
       <c r="D12" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="40" t="inlineStr">
+      <c r="E12" s="49" t="inlineStr">
         <is>
           <t>IAS 2 Cost / NRV</t>
         </is>
@@ -17777,7 +17466,7 @@
       <c r="D13" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="40" t="inlineStr">
+      <c r="E13" s="49" t="inlineStr">
         <is>
           <t>IFRS 15 Unbilled Revenue</t>
         </is>
@@ -17800,7 +17489,7 @@
       <c r="D14" s="21" t="n">
         <v>3374668</v>
       </c>
-      <c r="E14" s="40" t="inlineStr">
+      <c r="E14" s="49" t="inlineStr">
         <is>
           <t>IFRS 9 Net of ECL</t>
         </is>
@@ -17823,28 +17512,28 @@
       <c r="D15" s="21" t="n">
         <v>52500</v>
       </c>
-      <c r="E15" s="40" t="inlineStr">
+      <c r="E15" s="49" t="inlineStr">
         <is>
           <t>Reconciled Bank Balances</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="45" t="inlineStr">
+      <c r="A16" s="51" t="inlineStr">
         <is>
           <t>TOTAL CURRENT ASSETS</t>
         </is>
       </c>
-      <c r="B16" s="46" t="n"/>
-      <c r="C16" s="47">
+      <c r="B16" s="52" t="n"/>
+      <c r="C16" s="53">
         <f>SUM(C12:C15)</f>
         <v/>
       </c>
-      <c r="D16" s="47">
+      <c r="D16" s="53">
         <f>SUM(D12:D15)</f>
         <v/>
       </c>
-      <c r="E16" s="48" t="inlineStr">
+      <c r="E16" s="54" t="inlineStr">
         <is>
           <t>TIED OUT</t>
         </is>
@@ -17877,10 +17566,10 @@
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="B18" s="44" t="n"/>
-      <c r="C18" s="44" t="n"/>
-      <c r="D18" s="44" t="n"/>
-      <c r="E18" s="44" t="n"/>
+      <c r="B18" s="50" t="n"/>
+      <c r="C18" s="50" t="n"/>
+      <c r="D18" s="50" t="n"/>
+      <c r="E18" s="50" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -17899,7 +17588,7 @@
       <c r="D19" s="21" t="n">
         <v>1000000</v>
       </c>
-      <c r="E19" s="40" t="inlineStr">
+      <c r="E19" s="49" t="inlineStr">
         <is>
           <t>1m Ordinary Shares @ ₦1</t>
         </is>
@@ -17922,28 +17611,28 @@
       <c r="D20" s="21" t="n">
         <v>2361708</v>
       </c>
-      <c r="E20" s="40" t="inlineStr">
+      <c r="E20" s="49" t="inlineStr">
         <is>
           <t>Cumulative Post-Tax Earnings</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="45" t="inlineStr">
+      <c r="A21" s="51" t="inlineStr">
         <is>
           <t>TOTAL EQUITY</t>
         </is>
       </c>
-      <c r="B21" s="46" t="n"/>
-      <c r="C21" s="47">
+      <c r="B21" s="52" t="n"/>
+      <c r="C21" s="53">
         <f>SUM(C19:C20)</f>
         <v/>
       </c>
-      <c r="D21" s="47">
+      <c r="D21" s="53">
         <f>SUM(D19:D20)</f>
         <v/>
       </c>
-      <c r="E21" s="48" t="inlineStr">
+      <c r="E21" s="54" t="inlineStr">
         <is>
           <t>TIED OUT</t>
         </is>
@@ -17955,10 +17644,10 @@
           <t>NON-CURRENT LIABILITIES</t>
         </is>
       </c>
-      <c r="B22" s="44" t="n"/>
-      <c r="C22" s="44" t="n"/>
-      <c r="D22" s="44" t="n"/>
-      <c r="E22" s="44" t="n"/>
+      <c r="B22" s="50" t="n"/>
+      <c r="C22" s="50" t="n"/>
+      <c r="D22" s="50" t="n"/>
+      <c r="E22" s="50" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -17977,28 +17666,28 @@
       <c r="D23" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="40" t="inlineStr">
+      <c r="E23" s="49" t="inlineStr">
         <is>
           <t>IAS 24 Related Party</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="45" t="inlineStr">
+      <c r="A24" s="51" t="inlineStr">
         <is>
           <t>TOTAL NON-CURRENT LIABILITIES</t>
         </is>
       </c>
-      <c r="B24" s="46" t="n"/>
-      <c r="C24" s="47">
+      <c r="B24" s="52" t="n"/>
+      <c r="C24" s="53">
         <f>C23</f>
         <v/>
       </c>
-      <c r="D24" s="47">
+      <c r="D24" s="53">
         <f>D23</f>
         <v/>
       </c>
-      <c r="E24" s="48" t="inlineStr">
+      <c r="E24" s="54" t="inlineStr">
         <is>
           <t>TIED OUT</t>
         </is>
@@ -18010,10 +17699,10 @@
           <t>CURRENT LIABILITIES</t>
         </is>
       </c>
-      <c r="B25" s="44" t="n"/>
-      <c r="C25" s="44" t="n"/>
-      <c r="D25" s="44" t="n"/>
-      <c r="E25" s="44" t="n"/>
+      <c r="B25" s="50" t="n"/>
+      <c r="C25" s="50" t="n"/>
+      <c r="D25" s="50" t="n"/>
+      <c r="E25" s="50" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -18032,7 +17721,7 @@
       <c r="D26" s="21" t="n">
         <v>75000</v>
       </c>
-      <c r="E26" s="40" t="inlineStr">
+      <c r="E26" s="49" t="inlineStr">
         <is>
           <t>Amortized Cost</t>
         </is>
@@ -18055,7 +17744,7 @@
       <c r="D27" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="40" t="inlineStr">
+      <c r="E27" s="49" t="inlineStr">
         <is>
           <t>IFRS 15 Customer Advances</t>
         </is>
@@ -18078,28 +17767,28 @@
       <c r="D28" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="40" t="inlineStr">
+      <c r="E28" s="49" t="inlineStr">
         <is>
           <t>CITA / TETFA Statutory</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="45" t="inlineStr">
+      <c r="A29" s="51" t="inlineStr">
         <is>
           <t>TOTAL CURRENT LIABILITIES</t>
         </is>
       </c>
-      <c r="B29" s="46" t="n"/>
-      <c r="C29" s="47">
+      <c r="B29" s="52" t="n"/>
+      <c r="C29" s="53">
         <f>SUM(C26:C28)</f>
         <v/>
       </c>
-      <c r="D29" s="47">
+      <c r="D29" s="53">
         <f>SUM(D26:D28)</f>
         <v/>
       </c>
-      <c r="E29" s="48" t="inlineStr">
+      <c r="E29" s="54" t="inlineStr">
         <is>
           <t>TIED OUT</t>
         </is>
@@ -18209,21 +17898,21 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="49" t="inlineStr">
+      <c r="A37" s="55" t="inlineStr">
         <is>
           <t>GROSS PROFIT</t>
         </is>
       </c>
-      <c r="B37" s="50" t="n"/>
-      <c r="C37" s="51">
+      <c r="B37" s="56" t="n"/>
+      <c r="C37" s="57">
         <f>SUM(C35:C36)</f>
         <v/>
       </c>
-      <c r="D37" s="51">
+      <c r="D37" s="57">
         <f>SUM(D35:D36)</f>
         <v/>
       </c>
-      <c r="E37" s="52" t="inlineStr">
+      <c r="E37" s="58" t="inlineStr">
         <is>
           <t>Gross Margin: 35.97%</t>
         </is>
@@ -18253,21 +17942,21 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="49" t="inlineStr">
+      <c r="A39" s="55" t="inlineStr">
         <is>
           <t>OPERATING PROFIT (EBIT)</t>
         </is>
       </c>
-      <c r="B39" s="50" t="n"/>
-      <c r="C39" s="51">
+      <c r="B39" s="56" t="n"/>
+      <c r="C39" s="57">
         <f>C37+C38</f>
         <v/>
       </c>
-      <c r="D39" s="51">
+      <c r="D39" s="57">
         <f>D37+D38</f>
         <v/>
       </c>
-      <c r="E39" s="52" t="inlineStr">
+      <c r="E39" s="58" t="inlineStr">
         <is>
           <t>Operating Margin: 19.29%</t>
         </is>
@@ -18297,21 +17986,21 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="49" t="inlineStr">
+      <c r="A41" s="55" t="inlineStr">
         <is>
           <t>PROFIT BEFORE TAXATION</t>
         </is>
       </c>
-      <c r="B41" s="50" t="n"/>
-      <c r="C41" s="51">
+      <c r="B41" s="56" t="n"/>
+      <c r="C41" s="57">
         <f>C39+C40</f>
         <v/>
       </c>
-      <c r="D41" s="51">
+      <c r="D41" s="57">
         <f>D39+D40</f>
         <v/>
       </c>
-      <c r="E41" s="52" t="inlineStr">
+      <c r="E41" s="58" t="inlineStr">
         <is>
           <t>Taxable Accounting Profit</t>
         </is>
@@ -18367,7 +18056,7 @@
           <t>OTHER COMPREHENSIVE INCOME</t>
         </is>
       </c>
-      <c r="B44" s="53" t="n"/>
+      <c r="B44" s="59" t="n"/>
       <c r="C44" s="21" t="n">
         <v>0</v>
       </c>
@@ -18438,15 +18127,15 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="45" t="inlineStr">
+      <c r="A50" s="51" t="inlineStr">
         <is>
           <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
-      <c r="B50" s="46" t="n"/>
-      <c r="C50" s="46" t="n"/>
-      <c r="D50" s="46" t="n"/>
-      <c r="E50" s="54" t="n"/>
+      <c r="B50" s="52" t="n"/>
+      <c r="C50" s="52" t="n"/>
+      <c r="D50" s="52" t="n"/>
+      <c r="E50" s="60" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -18477,9 +18166,9 @@
           <t>Adjustments for non-cash items:</t>
         </is>
       </c>
-      <c r="B52" s="53" t="n"/>
-      <c r="C52" s="53" t="n"/>
-      <c r="D52" s="53" t="n"/>
+      <c r="B52" s="59" t="n"/>
+      <c r="C52" s="59" t="n"/>
+      <c r="D52" s="59" t="n"/>
       <c r="E52" s="7" t="n"/>
     </row>
     <row r="53">
@@ -18557,7 +18246,7 @@
           <t>Operating profit before working capital changes</t>
         </is>
       </c>
-      <c r="B56" s="53" t="n"/>
+      <c r="B56" s="59" t="n"/>
       <c r="C56" s="21">
         <f>SUM(C51:C55)</f>
         <v/>
@@ -18578,9 +18267,9 @@
           <t>Working capital changes:</t>
         </is>
       </c>
-      <c r="B57" s="53" t="n"/>
-      <c r="C57" s="53" t="n"/>
-      <c r="D57" s="53" t="n"/>
+      <c r="B57" s="59" t="n"/>
+      <c r="C57" s="59" t="n"/>
+      <c r="D57" s="59" t="n"/>
       <c r="E57" s="7" t="n"/>
     </row>
     <row r="58">
@@ -18704,7 +18393,7 @@
           <t>Cash generated from / (used in) operations</t>
         </is>
       </c>
-      <c r="B63" s="53" t="n"/>
+      <c r="B63" s="59" t="n"/>
       <c r="C63" s="21">
         <f>C56+SUM(C58:C62)</f>
         <v/>
@@ -18771,7 +18460,7 @@
           <t>Net cash flows from / (used in) operating activities</t>
         </is>
       </c>
-      <c r="B66" s="44" t="n"/>
+      <c r="B66" s="50" t="n"/>
       <c r="C66" s="17">
         <f>C63+C64+C65</f>
         <v/>
@@ -18787,15 +18476,15 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="45" t="inlineStr">
+      <c r="A67" s="51" t="inlineStr">
         <is>
           <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
-      <c r="B67" s="46" t="n"/>
-      <c r="C67" s="46" t="n"/>
-      <c r="D67" s="46" t="n"/>
-      <c r="E67" s="54" t="n"/>
+      <c r="B67" s="52" t="n"/>
+      <c r="C67" s="52" t="n"/>
+      <c r="D67" s="52" t="n"/>
+      <c r="E67" s="60" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -18826,7 +18515,7 @@
           <t>Net cash flows used in investing activities</t>
         </is>
       </c>
-      <c r="B69" s="44" t="n"/>
+      <c r="B69" s="50" t="n"/>
       <c r="C69" s="17">
         <f>C68</f>
         <v/>
@@ -18842,15 +18531,15 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="45" t="inlineStr">
+      <c r="A70" s="51" t="inlineStr">
         <is>
           <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
-      <c r="B70" s="46" t="n"/>
-      <c r="C70" s="46" t="n"/>
-      <c r="D70" s="46" t="n"/>
-      <c r="E70" s="54" t="n"/>
+      <c r="B70" s="52" t="n"/>
+      <c r="C70" s="52" t="n"/>
+      <c r="D70" s="52" t="n"/>
+      <c r="E70" s="60" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -18881,7 +18570,7 @@
           <t>Net cash flows from financing activities</t>
         </is>
       </c>
-      <c r="B72" s="44" t="n"/>
+      <c r="B72" s="50" t="n"/>
       <c r="C72" s="17">
         <f>C71</f>
         <v/>
@@ -18902,7 +18591,7 @@
           <t>Net increase in cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B73" s="53" t="n"/>
+      <c r="B73" s="59" t="n"/>
       <c r="C73" s="21">
         <f>C66+C69+C72</f>
         <v/>
@@ -18946,7 +18635,7 @@
           <t>CASH AND CASH EQUIVALENTS AT 31 DECEMBER</t>
         </is>
       </c>
-      <c r="B75" s="37" t="inlineStr">
+      <c r="B75" s="45" t="inlineStr">
         <is>
           <t>Note 11</t>
         </is>
@@ -18959,7 +18648,7 @@
         <f>D73+D74</f>
         <v/>
       </c>
-      <c r="E75" s="55" t="inlineStr">
+      <c r="E75" s="61" t="inlineStr">
         <is>
           <t>TIED TO SFP NOTE 11</t>
         </is>
@@ -19050,9 +18739,9 @@
           <t>Corporate Profile, RC 1526224, Registered in Nigeria under CAMA</t>
         </is>
       </c>
-      <c r="D5" s="44" t="n"/>
-      <c r="E5" s="44" t="n"/>
-      <c r="F5" s="41" t="inlineStr">
+      <c r="D5" s="50" t="n"/>
+      <c r="E5" s="50" t="n"/>
+      <c r="F5" s="48" t="inlineStr">
         <is>
           <t>IAS 1.51</t>
         </is>
@@ -19074,9 +18763,9 @@
           <t>Compliance with full IFRS, FRCN &amp; historical cost convention</t>
         </is>
       </c>
-      <c r="D6" s="53" t="n"/>
-      <c r="E6" s="53" t="n"/>
-      <c r="F6" s="40" t="inlineStr">
+      <c r="D6" s="59" t="n"/>
+      <c r="E6" s="59" t="n"/>
+      <c r="F6" s="49" t="inlineStr">
         <is>
           <t>IAS 1.112</t>
         </is>
@@ -19104,7 +18793,7 @@
       <c r="E7" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="41" t="inlineStr">
+      <c r="F7" s="48" t="inlineStr">
         <is>
           <t>IFRS 15 Over Time</t>
         </is>
@@ -19132,7 +18821,7 @@
       <c r="E8" s="21" t="n">
         <v>8500000</v>
       </c>
-      <c r="F8" s="40" t="inlineStr">
+      <c r="F8" s="49" t="inlineStr">
         <is>
           <t>IFRS 15 Point in Time</t>
         </is>
@@ -19160,14 +18849,14 @@
       <c r="E9" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="41" t="inlineStr">
+      <c r="F9" s="48" t="inlineStr">
         <is>
           <t>IFRS 15 Over Time</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>Note 3</t>
         </is>
@@ -19218,7 +18907,7 @@
       <c r="E11" s="22" t="n">
         <v>2400000</v>
       </c>
-      <c r="F11" s="41" t="inlineStr">
+      <c r="F11" s="48" t="inlineStr">
         <is>
           <t>IAS 2 Direct Materials</t>
         </is>
@@ -19246,7 +18935,7 @@
       <c r="E12" s="21" t="n">
         <v>2800000</v>
       </c>
-      <c r="F12" s="40" t="inlineStr">
+      <c r="F12" s="49" t="inlineStr">
         <is>
           <t>IAS 2 Inventory Cost</t>
         </is>
@@ -19274,14 +18963,14 @@
       <c r="E13" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="41" t="inlineStr">
+      <c r="F13" s="48" t="inlineStr">
         <is>
           <t>IAS 2 Direct Labor</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="47" t="inlineStr">
         <is>
           <t>Note 4</t>
         </is>
@@ -19332,7 +19021,7 @@
       <c r="E15" s="22" t="n">
         <v>1200000</v>
       </c>
-      <c r="F15" s="41" t="inlineStr">
+      <c r="F15" s="48" t="inlineStr">
         <is>
           <t>IAS 19 Employee Costs</t>
         </is>
@@ -19360,7 +19049,7 @@
       <c r="E16" s="21" t="n">
         <v>450000</v>
       </c>
-      <c r="F16" s="40" t="inlineStr">
+      <c r="F16" s="49" t="inlineStr">
         <is>
           <t>Operating Overheads</t>
         </is>
@@ -19388,7 +19077,7 @@
       <c r="E17" s="22" t="n">
         <v>300000</v>
       </c>
-      <c r="F17" s="41" t="inlineStr">
+      <c r="F17" s="48" t="inlineStr">
         <is>
           <t>Professional Services</t>
         </is>
@@ -19416,7 +19105,7 @@
       <c r="E18" s="21" t="n">
         <v>50000</v>
       </c>
-      <c r="F18" s="40" t="inlineStr">
+      <c r="F18" s="49" t="inlineStr">
         <is>
           <t>Audit Fees Accrual</t>
         </is>
@@ -19444,7 +19133,7 @@
       <c r="E19" s="22" t="n">
         <v>85000</v>
       </c>
-      <c r="F19" s="41" t="inlineStr">
+      <c r="F19" s="48" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -19472,7 +19161,7 @@
       <c r="E20" s="21" t="n">
         <v>180000</v>
       </c>
-      <c r="F20" s="40" t="inlineStr">
+      <c r="F20" s="49" t="inlineStr">
         <is>
           <t>Transport &amp; Travel</t>
         </is>
@@ -19500,7 +19189,7 @@
       <c r="E21" s="22" t="n">
         <v>4770</v>
       </c>
-      <c r="F21" s="41" t="inlineStr">
+      <c r="F21" s="48" t="inlineStr">
         <is>
           <t>IAS 16 Depreciation</t>
         </is>
@@ -19528,7 +19217,7 @@
       <c r="E22" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="40" t="inlineStr">
+      <c r="F22" s="49" t="inlineStr">
         <is>
           <t>IFRS 9 Impairment</t>
         </is>
@@ -19556,14 +19245,14 @@
       <c r="E23" s="22" t="n">
         <v>318522</v>
       </c>
-      <c r="F23" s="41" t="inlineStr">
+      <c r="F23" s="48" t="inlineStr">
         <is>
           <t>General Administration</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="43" t="inlineStr">
+      <c r="A24" s="47" t="inlineStr">
         <is>
           <t>Note 5</t>
         </is>
@@ -19614,14 +19303,14 @@
       <c r="E25" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="41" t="inlineStr">
+      <c r="F25" s="48" t="inlineStr">
         <is>
           <t>IAS 23 Borrowing Costs</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="43" t="inlineStr">
+      <c r="A26" s="47" t="inlineStr">
         <is>
           <t>Note 6</t>
         </is>
@@ -19672,14 +19361,14 @@
       <c r="E27" s="22" t="n">
         <v>9540</v>
       </c>
-      <c r="F27" s="41" t="inlineStr">
+      <c r="F27" s="48" t="inlineStr">
         <is>
           <t>IAS 16 Carrying Amount</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="43" t="inlineStr">
+      <c r="A28" s="47" t="inlineStr">
         <is>
           <t>Note 7</t>
         </is>
@@ -19730,7 +19419,7 @@
       <c r="E29" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F29" s="41" t="inlineStr">
+      <c r="F29" s="48" t="inlineStr">
         <is>
           <t>IAS 2 Lower of Cost/NRV</t>
         </is>
@@ -19758,14 +19447,14 @@
       <c r="E30" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="40" t="inlineStr">
+      <c r="F30" s="49" t="inlineStr">
         <is>
           <t>IAS 2 Lower of Cost/NRV</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="43" t="inlineStr">
+      <c r="A31" s="47" t="inlineStr">
         <is>
           <t>Note 8</t>
         </is>
@@ -19816,14 +19505,14 @@
       <c r="E32" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F32" s="40" t="inlineStr">
+      <c r="F32" s="49" t="inlineStr">
         <is>
           <t>IFRS 15 Unbilled Asset</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="43" t="inlineStr">
+      <c r="A33" s="47" t="inlineStr">
         <is>
           <t>Note 9</t>
         </is>
@@ -19874,7 +19563,7 @@
       <c r="E34" s="21" t="n">
         <v>2850000</v>
       </c>
-      <c r="F34" s="40" t="inlineStr">
+      <c r="F34" s="49" t="inlineStr">
         <is>
           <t>Amortized Cost</t>
         </is>
@@ -19902,7 +19591,7 @@
       <c r="E35" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F35" s="41" t="inlineStr">
+      <c r="F35" s="48" t="inlineStr">
         <is>
           <t>IFRS 9 ECL Provision</t>
         </is>
@@ -19930,7 +19619,7 @@
       <c r="E36" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F36" s="40" t="inlineStr">
+      <c r="F36" s="49" t="inlineStr">
         <is>
           <t>FIRS Credit Notes</t>
         </is>
@@ -19958,14 +19647,14 @@
       <c r="E37" s="22" t="n">
         <v>524668</v>
       </c>
-      <c r="F37" s="41" t="inlineStr">
+      <c r="F37" s="48" t="inlineStr">
         <is>
           <t>Operating Prepayments</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="43" t="inlineStr">
+      <c r="A38" s="47" t="inlineStr">
         <is>
           <t>Note 10</t>
         </is>
@@ -20016,7 +19705,7 @@
       <c r="E39" s="22" t="n">
         <v>52500</v>
       </c>
-      <c r="F39" s="41" t="inlineStr">
+      <c r="F39" s="48" t="inlineStr">
         <is>
           <t>Primary Operating A/C</t>
         </is>
@@ -20044,7 +19733,7 @@
       <c r="E40" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F40" s="40" t="inlineStr">
+      <c r="F40" s="49" t="inlineStr">
         <is>
           <t>Site Collection A/C</t>
         </is>
@@ -20072,14 +19761,14 @@
       <c r="E41" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="41" t="inlineStr">
+      <c r="F41" s="48" t="inlineStr">
         <is>
           <t>Disbursement A/C</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="43" t="inlineStr">
+      <c r="A42" s="47" t="inlineStr">
         <is>
           <t>Note 11</t>
         </is>
@@ -20130,14 +19819,14 @@
       <c r="E43" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="41" t="inlineStr">
+      <c r="F43" s="48" t="inlineStr">
         <is>
           <t>IFRS 15 Advances</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="43" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>Note 13</t>
         </is>
@@ -20188,7 +19877,7 @@
       <c r="E45" s="22" t="n">
         <v>25000</v>
       </c>
-      <c r="F45" s="41" t="inlineStr">
+      <c r="F45" s="48" t="inlineStr">
         <is>
           <t>Trade Creditors</t>
         </is>
@@ -20216,7 +19905,7 @@
       <c r="E46" s="21" t="n">
         <v>50000</v>
       </c>
-      <c r="F46" s="40" t="inlineStr">
+      <c r="F46" s="49" t="inlineStr">
         <is>
           <t>Audit Accrual</t>
         </is>
@@ -20244,14 +19933,14 @@
       <c r="E47" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F47" s="41" t="inlineStr">
+      <c r="F47" s="48" t="inlineStr">
         <is>
           <t>Sundry Accruals</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="43" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>Note 14</t>
         </is>
@@ -20302,14 +19991,14 @@
       <c r="E49" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F49" s="41" t="inlineStr">
+      <c r="F49" s="48" t="inlineStr">
         <is>
           <t>IAS 12 Net Asset</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="43" t="inlineStr">
+      <c r="A50" s="47" t="inlineStr">
         <is>
           <t>Note 15</t>
         </is>
@@ -20360,7 +20049,7 @@
       <c r="E51" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F51" s="41" t="inlineStr">
+      <c r="F51" s="48" t="inlineStr">
         <is>
           <t>20% CIT Medium Co</t>
         </is>
@@ -20388,7 +20077,7 @@
       <c r="E52" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F52" s="40" t="inlineStr">
+      <c r="F52" s="49" t="inlineStr">
         <is>
           <t>3% TETFA Rate</t>
         </is>
@@ -20416,14 +20105,14 @@
       <c r="E53" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F53" s="41" t="inlineStr">
+      <c r="F53" s="48" t="inlineStr">
         <is>
           <t>0.005% of PBT</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="43" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>Note 16</t>
         </is>
@@ -20474,14 +20163,14 @@
       <c r="E55" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F55" s="41" t="inlineStr">
+      <c r="F55" s="48" t="inlineStr">
         <is>
           <t>IAS 24 Related Party</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="43" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>Note 17</t>
         </is>
@@ -20532,14 +20221,14 @@
       <c r="E57" s="22" t="n">
         <v>1000000</v>
       </c>
-      <c r="F57" s="41" t="inlineStr">
+      <c r="F57" s="48" t="inlineStr">
         <is>
           <t>Authorized &amp; Issued</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="43" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>Note 18</t>
         </is>
@@ -20590,14 +20279,14 @@
       <c r="E59" s="22" t="n">
         <v>2361708</v>
       </c>
-      <c r="F59" s="41" t="inlineStr">
+      <c r="F59" s="48" t="inlineStr">
         <is>
           <t>SOCE Roll-Forward</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="43" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>Note 19</t>
         </is>
@@ -20709,10 +20398,10 @@
           <t>NON-CURRENT ASSETS</t>
         </is>
       </c>
-      <c r="B7" s="44" t="n"/>
-      <c r="C7" s="44" t="n"/>
-      <c r="D7" s="44" t="n"/>
-      <c r="E7" s="44" t="n"/>
+      <c r="B7" s="50" t="n"/>
+      <c r="C7" s="50" t="n"/>
+      <c r="D7" s="50" t="n"/>
+      <c r="E7" s="50" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -20731,7 +20420,7 @@
       <c r="D8" s="21" t="n">
         <v>1424540</v>
       </c>
-      <c r="E8" s="40" t="inlineStr">
+      <c r="E8" s="49" t="inlineStr">
         <is>
           <t>IAS 16 Carrying Amount</t>
         </is>
@@ -20754,28 +20443,28 @@
       <c r="D9" s="21" t="n">
         <v>32000</v>
       </c>
-      <c r="E9" s="40" t="inlineStr">
+      <c r="E9" s="49" t="inlineStr">
         <is>
           <t>IAS 12 Temporary Differences</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="45" t="inlineStr">
+      <c r="A10" s="51" t="inlineStr">
         <is>
           <t>TOTAL NON-CURRENT ASSETS</t>
         </is>
       </c>
-      <c r="B10" s="46" t="n"/>
-      <c r="C10" s="47">
+      <c r="B10" s="52" t="n"/>
+      <c r="C10" s="53">
         <f>SUM(C8:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="47">
+      <c r="D10" s="53">
         <f>SUM(D8:D9)</f>
         <v/>
       </c>
-      <c r="E10" s="48" t="inlineStr">
+      <c r="E10" s="54" t="inlineStr">
         <is>
           <t>TIED OUT</t>
         </is>
@@ -20787,10 +20476,10 @@
           <t>CURRENT ASSETS</t>
         </is>
       </c>
-      <c r="B11" s="44" t="n"/>
-      <c r="C11" s="44" t="n"/>
-      <c r="D11" s="44" t="n"/>
-      <c r="E11" s="44" t="n"/>
+      <c r="B11" s="50" t="n"/>
+      <c r="C11" s="50" t="n"/>
+      <c r="D11" s="50" t="n"/>
+      <c r="E11" s="50" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -20809,7 +20498,7 @@
       <c r="D12" s="21" t="n">
         <v>8650000</v>
       </c>
-      <c r="E12" s="40" t="inlineStr">
+      <c r="E12" s="49" t="inlineStr">
         <is>
           <t>IAS 2 Cost / NRV</t>
         </is>
@@ -20832,7 +20521,7 @@
       <c r="D13" s="21" t="n">
         <v>2400000</v>
       </c>
-      <c r="E13" s="40" t="inlineStr">
+      <c r="E13" s="49" t="inlineStr">
         <is>
           <t>IFRS 15 Unbilled Revenue</t>
         </is>
@@ -20855,7 +20544,7 @@
       <c r="D14" s="21" t="n">
         <v>5015000</v>
       </c>
-      <c r="E14" s="40" t="inlineStr">
+      <c r="E14" s="49" t="inlineStr">
         <is>
           <t>IFRS 9 Net of ECL</t>
         </is>
@@ -20878,28 +20567,28 @@
       <c r="D15" s="21" t="n">
         <v>2842403</v>
       </c>
-      <c r="E15" s="40" t="inlineStr">
+      <c r="E15" s="49" t="inlineStr">
         <is>
           <t>Reconciled Bank Balances</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="45" t="inlineStr">
+      <c r="A16" s="51" t="inlineStr">
         <is>
           <t>TOTAL CURRENT ASSETS</t>
         </is>
       </c>
-      <c r="B16" s="46" t="n"/>
-      <c r="C16" s="47">
+      <c r="B16" s="52" t="n"/>
+      <c r="C16" s="53">
         <f>SUM(C12:C15)</f>
         <v/>
       </c>
-      <c r="D16" s="47">
+      <c r="D16" s="53">
         <f>SUM(D12:D15)</f>
         <v/>
       </c>
-      <c r="E16" s="48" t="inlineStr">
+      <c r="E16" s="54" t="inlineStr">
         <is>
           <t>TIED OUT</t>
         </is>
@@ -20932,10 +20621,10 @@
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="B18" s="44" t="n"/>
-      <c r="C18" s="44" t="n"/>
-      <c r="D18" s="44" t="n"/>
-      <c r="E18" s="44" t="n"/>
+      <c r="B18" s="50" t="n"/>
+      <c r="C18" s="50" t="n"/>
+      <c r="D18" s="50" t="n"/>
+      <c r="E18" s="50" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -20954,7 +20643,7 @@
       <c r="D19" s="21" t="n">
         <v>1000000</v>
       </c>
-      <c r="E19" s="40" t="inlineStr">
+      <c r="E19" s="49" t="inlineStr">
         <is>
           <t>1m Ordinary Shares @ ₦1</t>
         </is>
@@ -20977,28 +20666,28 @@
       <c r="D20" s="21" t="n">
         <v>7961943</v>
       </c>
-      <c r="E20" s="40" t="inlineStr">
+      <c r="E20" s="49" t="inlineStr">
         <is>
           <t>Cumulative Post-Tax Earnings</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="45" t="inlineStr">
+      <c r="A21" s="51" t="inlineStr">
         <is>
           <t>TOTAL EQUITY</t>
         </is>
       </c>
-      <c r="B21" s="46" t="n"/>
-      <c r="C21" s="47">
+      <c r="B21" s="52" t="n"/>
+      <c r="C21" s="53">
         <f>SUM(C19:C20)</f>
         <v/>
       </c>
-      <c r="D21" s="47">
+      <c r="D21" s="53">
         <f>SUM(D19:D20)</f>
         <v/>
       </c>
-      <c r="E21" s="48" t="inlineStr">
+      <c r="E21" s="54" t="inlineStr">
         <is>
           <t>TIED OUT</t>
         </is>
@@ -21010,10 +20699,10 @@
           <t>NON-CURRENT LIABILITIES</t>
         </is>
       </c>
-      <c r="B22" s="44" t="n"/>
-      <c r="C22" s="44" t="n"/>
-      <c r="D22" s="44" t="n"/>
-      <c r="E22" s="44" t="n"/>
+      <c r="B22" s="50" t="n"/>
+      <c r="C22" s="50" t="n"/>
+      <c r="D22" s="50" t="n"/>
+      <c r="E22" s="50" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -21032,7 +20721,7 @@
       <c r="D23" s="21" t="n">
         <v>4500000</v>
       </c>
-      <c r="E23" s="40" t="inlineStr">
+      <c r="E23" s="49" t="inlineStr">
         <is>
           <t>IAS 24 Related Party</t>
         </is>
@@ -21055,28 +20744,28 @@
       <c r="D24" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="40" t="inlineStr">
+      <c r="E24" s="49" t="inlineStr">
         <is>
           <t>IAS 12 Temporary Differences</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="45" t="inlineStr">
+      <c r="A25" s="51" t="inlineStr">
         <is>
           <t>TOTAL NON-CURRENT LIABILITIES</t>
         </is>
       </c>
-      <c r="B25" s="46" t="n"/>
-      <c r="C25" s="47">
+      <c r="B25" s="52" t="n"/>
+      <c r="C25" s="53">
         <f>SUM(C23:C24)</f>
         <v/>
       </c>
-      <c r="D25" s="47">
+      <c r="D25" s="53">
         <f>SUM(D23:D24)</f>
         <v/>
       </c>
-      <c r="E25" s="48" t="inlineStr">
+      <c r="E25" s="54" t="inlineStr">
         <is>
           <t>TIED OUT</t>
         </is>
@@ -21088,10 +20777,10 @@
           <t>CURRENT LIABILITIES</t>
         </is>
       </c>
-      <c r="B26" s="44" t="n"/>
-      <c r="C26" s="44" t="n"/>
-      <c r="D26" s="44" t="n"/>
-      <c r="E26" s="44" t="n"/>
+      <c r="B26" s="50" t="n"/>
+      <c r="C26" s="50" t="n"/>
+      <c r="D26" s="50" t="n"/>
+      <c r="E26" s="50" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -21110,7 +20799,7 @@
       <c r="D27" s="21" t="n">
         <v>2770235</v>
       </c>
-      <c r="E27" s="40" t="inlineStr">
+      <c r="E27" s="49" t="inlineStr">
         <is>
           <t>Amortized Cost</t>
         </is>
@@ -21133,7 +20822,7 @@
       <c r="D28" s="21" t="n">
         <v>2400000</v>
       </c>
-      <c r="E28" s="40" t="inlineStr">
+      <c r="E28" s="49" t="inlineStr">
         <is>
           <t>IFRS 15 Customer Advances</t>
         </is>
@@ -21156,28 +20845,28 @@
       <c r="D29" s="21" t="n">
         <v>1731765</v>
       </c>
-      <c r="E29" s="40" t="inlineStr">
+      <c r="E29" s="49" t="inlineStr">
         <is>
           <t>CITA / TETFA Statutory</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="45" t="inlineStr">
+      <c r="A30" s="51" t="inlineStr">
         <is>
           <t>TOTAL CURRENT LIABILITIES</t>
         </is>
       </c>
-      <c r="B30" s="46" t="n"/>
-      <c r="C30" s="47">
+      <c r="B30" s="52" t="n"/>
+      <c r="C30" s="53">
         <f>SUM(C27:C29)</f>
         <v/>
       </c>
-      <c r="D30" s="47">
+      <c r="D30" s="53">
         <f>SUM(D27:D29)</f>
         <v/>
       </c>
-      <c r="E30" s="48" t="inlineStr">
+      <c r="E30" s="54" t="inlineStr">
         <is>
           <t>TIED OUT</t>
         </is>
@@ -21287,21 +20976,21 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="49" t="inlineStr">
+      <c r="A38" s="55" t="inlineStr">
         <is>
           <t>GROSS PROFIT</t>
         </is>
       </c>
-      <c r="B38" s="50" t="n"/>
-      <c r="C38" s="51">
+      <c r="B38" s="56" t="n"/>
+      <c r="C38" s="57">
         <f>SUM(C36:C37)</f>
         <v/>
       </c>
-      <c r="D38" s="51">
+      <c r="D38" s="57">
         <f>SUM(D36:D37)</f>
         <v/>
       </c>
-      <c r="E38" s="52" t="inlineStr">
+      <c r="E38" s="58" t="inlineStr">
         <is>
           <t>Gross Margin: 35.36%</t>
         </is>
@@ -21331,21 +21020,21 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="49" t="inlineStr">
+      <c r="A40" s="55" t="inlineStr">
         <is>
           <t>OPERATING PROFIT (EBIT)</t>
         </is>
       </c>
-      <c r="B40" s="50" t="n"/>
-      <c r="C40" s="51">
+      <c r="B40" s="56" t="n"/>
+      <c r="C40" s="57">
         <f>C38+C39</f>
         <v/>
       </c>
-      <c r="D40" s="51">
+      <c r="D40" s="57">
         <f>D38+D39</f>
         <v/>
       </c>
-      <c r="E40" s="52" t="inlineStr">
+      <c r="E40" s="58" t="inlineStr">
         <is>
           <t>Operating Margin: 20.02%</t>
         </is>
@@ -21375,21 +21064,21 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="49" t="inlineStr">
+      <c r="A42" s="55" t="inlineStr">
         <is>
           <t>PROFIT BEFORE TAXATION</t>
         </is>
       </c>
-      <c r="B42" s="50" t="n"/>
-      <c r="C42" s="51">
+      <c r="B42" s="56" t="n"/>
+      <c r="C42" s="57">
         <f>C40+C41</f>
         <v/>
       </c>
-      <c r="D42" s="51">
+      <c r="D42" s="57">
         <f>D40+D41</f>
         <v/>
       </c>
-      <c r="E42" s="52" t="inlineStr">
+      <c r="E42" s="58" t="inlineStr">
         <is>
           <t>Taxable Accounting Profit</t>
         </is>
@@ -21445,7 +21134,7 @@
           <t>OTHER COMPREHENSIVE INCOME</t>
         </is>
       </c>
-      <c r="B45" s="44" t="n"/>
+      <c r="B45" s="50" t="n"/>
       <c r="C45" s="22" t="n">
         <v>0</v>
       </c>
@@ -21516,15 +21205,15 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="45" t="inlineStr">
+      <c r="A51" s="51" t="inlineStr">
         <is>
           <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
-      <c r="B51" s="46" t="n"/>
-      <c r="C51" s="46" t="n"/>
-      <c r="D51" s="46" t="n"/>
-      <c r="E51" s="54" t="n"/>
+      <c r="B51" s="52" t="n"/>
+      <c r="C51" s="52" t="n"/>
+      <c r="D51" s="52" t="n"/>
+      <c r="E51" s="60" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -21555,9 +21244,9 @@
           <t>Adjustments for non-cash items:</t>
         </is>
       </c>
-      <c r="B53" s="53" t="n"/>
-      <c r="C53" s="53" t="n"/>
-      <c r="D53" s="53" t="n"/>
+      <c r="B53" s="59" t="n"/>
+      <c r="C53" s="59" t="n"/>
+      <c r="D53" s="59" t="n"/>
       <c r="E53" s="7" t="n"/>
     </row>
     <row r="54">
@@ -21635,7 +21324,7 @@
           <t>Operating profit before working capital changes</t>
         </is>
       </c>
-      <c r="B57" s="53" t="n"/>
+      <c r="B57" s="59" t="n"/>
       <c r="C57" s="21">
         <f>SUM(C52:C56)</f>
         <v/>
@@ -21656,9 +21345,9 @@
           <t>Working capital changes:</t>
         </is>
       </c>
-      <c r="B58" s="53" t="n"/>
-      <c r="C58" s="53" t="n"/>
-      <c r="D58" s="53" t="n"/>
+      <c r="B58" s="59" t="n"/>
+      <c r="C58" s="59" t="n"/>
+      <c r="D58" s="59" t="n"/>
       <c r="E58" s="7" t="n"/>
     </row>
     <row r="59">
@@ -21782,7 +21471,7 @@
           <t>Cash generated from operations</t>
         </is>
       </c>
-      <c r="B64" s="53" t="n"/>
+      <c r="B64" s="59" t="n"/>
       <c r="C64" s="21">
         <f>C57+SUM(C59:C63)</f>
         <v/>
@@ -21849,7 +21538,7 @@
           <t>Net cash flows from operating activities</t>
         </is>
       </c>
-      <c r="B67" s="44" t="n"/>
+      <c r="B67" s="50" t="n"/>
       <c r="C67" s="17">
         <f>C64+C65+C66</f>
         <v/>
@@ -21865,15 +21554,15 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="45" t="inlineStr">
+      <c r="A68" s="51" t="inlineStr">
         <is>
           <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
-      <c r="B68" s="46" t="n"/>
-      <c r="C68" s="46" t="n"/>
-      <c r="D68" s="46" t="n"/>
-      <c r="E68" s="54" t="n"/>
+      <c r="B68" s="52" t="n"/>
+      <c r="C68" s="52" t="n"/>
+      <c r="D68" s="52" t="n"/>
+      <c r="E68" s="60" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -21904,7 +21593,7 @@
           <t>Net cash flows used in investing activities</t>
         </is>
       </c>
-      <c r="B70" s="44" t="n"/>
+      <c r="B70" s="50" t="n"/>
       <c r="C70" s="17">
         <f>C69</f>
         <v/>
@@ -21920,15 +21609,15 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="45" t="inlineStr">
+      <c r="A71" s="51" t="inlineStr">
         <is>
           <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
-      <c r="B71" s="46" t="n"/>
-      <c r="C71" s="46" t="n"/>
-      <c r="D71" s="46" t="n"/>
-      <c r="E71" s="54" t="n"/>
+      <c r="B71" s="52" t="n"/>
+      <c r="C71" s="52" t="n"/>
+      <c r="D71" s="52" t="n"/>
+      <c r="E71" s="60" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -21959,7 +21648,7 @@
           <t>Net cash flows from financing activities</t>
         </is>
       </c>
-      <c r="B73" s="44" t="n"/>
+      <c r="B73" s="50" t="n"/>
       <c r="C73" s="17">
         <f>C72</f>
         <v/>
@@ -21980,7 +21669,7 @@
           <t>Net increase in cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B74" s="53" t="n"/>
+      <c r="B74" s="59" t="n"/>
       <c r="C74" s="21">
         <f>C67+C70+C73</f>
         <v/>
@@ -22024,7 +21713,7 @@
           <t>CASH AND CASH EQUIVALENTS AT 31 DECEMBER</t>
         </is>
       </c>
-      <c r="B76" s="37" t="inlineStr">
+      <c r="B76" s="45" t="inlineStr">
         <is>
           <t>Note 11</t>
         </is>
@@ -22037,7 +21726,7 @@
         <f>D74+D75</f>
         <v/>
       </c>
-      <c r="E76" s="55" t="inlineStr">
+      <c r="E76" s="61" t="inlineStr">
         <is>
           <t>TIED TO SFP NOTE 11</t>
         </is>
@@ -22054,20 +21743,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="103" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="81" customWidth="1" min="2" max="2"/>
     <col width="39" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="72" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="81" customWidth="1" min="5" max="5"/>
+    <col width="51" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
     <col width="29" customWidth="1" min="10" max="10"/>
-    <col width="59" customWidth="1" min="11" max="11"/>
+    <col width="100" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22909,6 +22598,61 @@
       <c r="K18" s="7" t="inlineStr">
         <is>
           <t>Monthly payroll reconstructed under PITA bands</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>SRC-15</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Sales &amp; Customers Register (BAAY_Sales_and_Customers_2022_2025_for_Audit.xlsx)</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Baay Projects Limited</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>FY 2022 - FY 2025</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Customer subscriptions, sales receipts, customer master, project cash receipts</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Revenue, Contract Liabilities, Trade Receivables</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>2584814000</v>
+      </c>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>Company Accountant / Client Relations</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>Extracted 860 sales receipts, 219 subscriptions, 241 customer master records &amp; reconciled to bank</t>
         </is>
       </c>
     </row>
@@ -22997,9 +22741,9 @@
           <t>Corporate Profile, RC 1526224, Registered in Nigeria under CAMA</t>
         </is>
       </c>
-      <c r="D5" s="44" t="n"/>
-      <c r="E5" s="44" t="n"/>
-      <c r="F5" s="41" t="inlineStr">
+      <c r="D5" s="50" t="n"/>
+      <c r="E5" s="50" t="n"/>
+      <c r="F5" s="48" t="inlineStr">
         <is>
           <t>IAS 1.51</t>
         </is>
@@ -23021,9 +22765,9 @@
           <t>Compliance with full IFRS, FRCN &amp; historical cost convention</t>
         </is>
       </c>
-      <c r="D6" s="53" t="n"/>
-      <c r="E6" s="53" t="n"/>
-      <c r="F6" s="40" t="inlineStr">
+      <c r="D6" s="59" t="n"/>
+      <c r="E6" s="59" t="n"/>
+      <c r="F6" s="49" t="inlineStr">
         <is>
           <t>IAS 1.112</t>
         </is>
@@ -23051,7 +22795,7 @@
       <c r="E7" s="22" t="n">
         <v>22000000</v>
       </c>
-      <c r="F7" s="41" t="inlineStr">
+      <c r="F7" s="48" t="inlineStr">
         <is>
           <t>IFRS 15 Over Time</t>
         </is>
@@ -23079,7 +22823,7 @@
       <c r="E8" s="21" t="n">
         <v>12500000</v>
       </c>
-      <c r="F8" s="40" t="inlineStr">
+      <c r="F8" s="49" t="inlineStr">
         <is>
           <t>IFRS 15 Point in Time</t>
         </is>
@@ -23107,14 +22851,14 @@
       <c r="E9" s="22" t="n">
         <v>4000000</v>
       </c>
-      <c r="F9" s="41" t="inlineStr">
+      <c r="F9" s="48" t="inlineStr">
         <is>
           <t>IFRS 15 Over Time</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>Note 3</t>
         </is>
@@ -23165,7 +22909,7 @@
       <c r="E11" s="22" t="n">
         <v>14200000</v>
       </c>
-      <c r="F11" s="41" t="inlineStr">
+      <c r="F11" s="48" t="inlineStr">
         <is>
           <t>IAS 2 Direct Materials</t>
         </is>
@@ -23193,7 +22937,7 @@
       <c r="E12" s="21" t="n">
         <v>8100000</v>
       </c>
-      <c r="F12" s="40" t="inlineStr">
+      <c r="F12" s="49" t="inlineStr">
         <is>
           <t>IAS 2 Inventory Cost</t>
         </is>
@@ -23221,14 +22965,14 @@
       <c r="E13" s="22" t="n">
         <v>2350000</v>
       </c>
-      <c r="F13" s="41" t="inlineStr">
+      <c r="F13" s="48" t="inlineStr">
         <is>
           <t>IAS 2 Direct Labor</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="47" t="inlineStr">
         <is>
           <t>Note 4</t>
         </is>
@@ -23279,7 +23023,7 @@
       <c r="E15" s="22" t="n">
         <v>2800000</v>
       </c>
-      <c r="F15" s="41" t="inlineStr">
+      <c r="F15" s="48" t="inlineStr">
         <is>
           <t>IAS 19 Employee Costs</t>
         </is>
@@ -23307,7 +23051,7 @@
       <c r="E16" s="21" t="n">
         <v>950000</v>
       </c>
-      <c r="F16" s="40" t="inlineStr">
+      <c r="F16" s="49" t="inlineStr">
         <is>
           <t>Operating Overheads</t>
         </is>
@@ -23335,7 +23079,7 @@
       <c r="E17" s="22" t="n">
         <v>650000</v>
       </c>
-      <c r="F17" s="41" t="inlineStr">
+      <c r="F17" s="48" t="inlineStr">
         <is>
           <t>Professional Services</t>
         </is>
@@ -23363,7 +23107,7 @@
       <c r="E18" s="21" t="n">
         <v>350000</v>
       </c>
-      <c r="F18" s="40" t="inlineStr">
+      <c r="F18" s="49" t="inlineStr">
         <is>
           <t>Audit Fees Accrual</t>
         </is>
@@ -23391,7 +23135,7 @@
       <c r="E19" s="22" t="n">
         <v>285000</v>
       </c>
-      <c r="F19" s="41" t="inlineStr">
+      <c r="F19" s="48" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -23419,7 +23163,7 @@
       <c r="E20" s="21" t="n">
         <v>420000</v>
       </c>
-      <c r="F20" s="40" t="inlineStr">
+      <c r="F20" s="49" t="inlineStr">
         <is>
           <t>Transport &amp; Travel</t>
         </is>
@@ -23447,7 +23191,7 @@
       <c r="E21" s="22" t="n">
         <v>385000</v>
       </c>
-      <c r="F21" s="41" t="inlineStr">
+      <c r="F21" s="48" t="inlineStr">
         <is>
           <t>IAS 16 Depreciation</t>
         </is>
@@ -23475,7 +23219,7 @@
       <c r="E22" s="21" t="n">
         <v>185000</v>
       </c>
-      <c r="F22" s="40" t="inlineStr">
+      <c r="F22" s="49" t="inlineStr">
         <is>
           <t>IFRS 9 Impairment</t>
         </is>
@@ -23503,14 +23247,14 @@
       <c r="E23" s="22" t="n">
         <v>400000</v>
       </c>
-      <c r="F23" s="41" t="inlineStr">
+      <c r="F23" s="48" t="inlineStr">
         <is>
           <t>General Administration</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="43" t="inlineStr">
+      <c r="A24" s="47" t="inlineStr">
         <is>
           <t>Note 5</t>
         </is>
@@ -23561,14 +23305,14 @@
       <c r="E25" s="22" t="n">
         <v>125000</v>
       </c>
-      <c r="F25" s="41" t="inlineStr">
+      <c r="F25" s="48" t="inlineStr">
         <is>
           <t>IAS 23 Borrowing Costs</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="43" t="inlineStr">
+      <c r="A26" s="47" t="inlineStr">
         <is>
           <t>Note 6</t>
         </is>
@@ -23619,7 +23363,7 @@
       <c r="E27" s="22" t="n">
         <v>1424540</v>
       </c>
-      <c r="F27" s="41" t="inlineStr">
+      <c r="F27" s="48" t="inlineStr">
         <is>
           <t>IAS 16 Carrying Amount</t>
         </is>
@@ -23647,14 +23391,14 @@
       <c r="E28" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="40" t="inlineStr">
+      <c r="F28" s="49" t="inlineStr">
         <is>
           <t>IAS 16 Carrying Amount</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="43" t="inlineStr">
+      <c r="A29" s="47" t="inlineStr">
         <is>
           <t>Note 7</t>
         </is>
@@ -23705,7 +23449,7 @@
       <c r="E30" s="21" t="n">
         <v>5400000</v>
       </c>
-      <c r="F30" s="40" t="inlineStr">
+      <c r="F30" s="49" t="inlineStr">
         <is>
           <t>IAS 2 Lower of Cost/NRV</t>
         </is>
@@ -23733,14 +23477,14 @@
       <c r="E31" s="22" t="n">
         <v>3250000</v>
       </c>
-      <c r="F31" s="41" t="inlineStr">
+      <c r="F31" s="48" t="inlineStr">
         <is>
           <t>IAS 2 Lower of Cost/NRV</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="43" t="inlineStr">
+      <c r="A32" s="47" t="inlineStr">
         <is>
           <t>Note 8</t>
         </is>
@@ -23791,14 +23535,14 @@
       <c r="E33" s="22" t="n">
         <v>2400000</v>
       </c>
-      <c r="F33" s="41" t="inlineStr">
+      <c r="F33" s="48" t="inlineStr">
         <is>
           <t>IFRS 15 Unbilled Asset</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="43" t="inlineStr">
+      <c r="A34" s="47" t="inlineStr">
         <is>
           <t>Note 9</t>
         </is>
@@ -23849,7 +23593,7 @@
       <c r="E35" s="22" t="n">
         <v>3650000</v>
       </c>
-      <c r="F35" s="41" t="inlineStr">
+      <c r="F35" s="48" t="inlineStr">
         <is>
           <t>Amortized Cost</t>
         </is>
@@ -23877,7 +23621,7 @@
       <c r="E36" s="21" t="n">
         <v>-185000</v>
       </c>
-      <c r="F36" s="40" t="inlineStr">
+      <c r="F36" s="49" t="inlineStr">
         <is>
           <t>IFRS 9 ECL Provision</t>
         </is>
@@ -23905,7 +23649,7 @@
       <c r="E37" s="22" t="n">
         <v>1100000</v>
       </c>
-      <c r="F37" s="41" t="inlineStr">
+      <c r="F37" s="48" t="inlineStr">
         <is>
           <t>FIRS Credit Notes</t>
         </is>
@@ -23933,14 +23677,14 @@
       <c r="E38" s="21" t="n">
         <v>450000</v>
       </c>
-      <c r="F38" s="40" t="inlineStr">
+      <c r="F38" s="49" t="inlineStr">
         <is>
           <t>Operating Prepayments</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="43" t="inlineStr">
+      <c r="A39" s="47" t="inlineStr">
         <is>
           <t>Note 10</t>
         </is>
@@ -23991,7 +23735,7 @@
       <c r="E40" s="21" t="n">
         <v>2215820</v>
       </c>
-      <c r="F40" s="40" t="inlineStr">
+      <c r="F40" s="49" t="inlineStr">
         <is>
           <t>Primary Operating A/C</t>
         </is>
@@ -24019,7 +23763,7 @@
       <c r="E41" s="22" t="n">
         <v>512410</v>
       </c>
-      <c r="F41" s="41" t="inlineStr">
+      <c r="F41" s="48" t="inlineStr">
         <is>
           <t>Site Collection A/C</t>
         </is>
@@ -24047,14 +23791,14 @@
       <c r="E42" s="21" t="n">
         <v>114173</v>
       </c>
-      <c r="F42" s="40" t="inlineStr">
+      <c r="F42" s="49" t="inlineStr">
         <is>
           <t>Disbursement A/C</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="43" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>Note 11</t>
         </is>
@@ -24105,14 +23849,14 @@
       <c r="E44" s="21" t="n">
         <v>2400000</v>
       </c>
-      <c r="F44" s="40" t="inlineStr">
+      <c r="F44" s="49" t="inlineStr">
         <is>
           <t>IFRS 15 Advances</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="43" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>Note 13</t>
         </is>
@@ -24163,7 +23907,7 @@
       <c r="E46" s="21" t="n">
         <v>2150000</v>
       </c>
-      <c r="F46" s="40" t="inlineStr">
+      <c r="F46" s="49" t="inlineStr">
         <is>
           <t>Trade Creditors</t>
         </is>
@@ -24191,7 +23935,7 @@
       <c r="E47" s="22" t="n">
         <v>375000</v>
       </c>
-      <c r="F47" s="41" t="inlineStr">
+      <c r="F47" s="48" t="inlineStr">
         <is>
           <t>Audit Accrual</t>
         </is>
@@ -24219,14 +23963,14 @@
       <c r="E48" s="21" t="n">
         <v>245235</v>
       </c>
-      <c r="F48" s="40" t="inlineStr">
+      <c r="F48" s="49" t="inlineStr">
         <is>
           <t>Sundry Accruals</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="43" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>Note 14</t>
         </is>
@@ -24277,14 +24021,14 @@
       <c r="E50" s="21" t="n">
         <v>32000</v>
       </c>
-      <c r="F50" s="40" t="inlineStr">
+      <c r="F50" s="49" t="inlineStr">
         <is>
           <t>IAS 12 Net Liability</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="43" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>Note 15</t>
         </is>
@@ -24335,7 +24079,7 @@
       <c r="E52" s="21" t="n">
         <v>1492000</v>
       </c>
-      <c r="F52" s="40" t="inlineStr">
+      <c r="F52" s="49" t="inlineStr">
         <is>
           <t>20% CIT Medium Co</t>
         </is>
@@ -24363,7 +24107,7 @@
       <c r="E53" s="22" t="n">
         <v>239400</v>
       </c>
-      <c r="F53" s="41" t="inlineStr">
+      <c r="F53" s="48" t="inlineStr">
         <is>
           <t>3% TETFA Rate</t>
         </is>
@@ -24391,14 +24135,14 @@
       <c r="E54" s="21" t="n">
         <v>365</v>
       </c>
-      <c r="F54" s="40" t="inlineStr">
+      <c r="F54" s="49" t="inlineStr">
         <is>
           <t>0.005% of PBT</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="43" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>Note 16</t>
         </is>
@@ -24449,14 +24193,14 @@
       <c r="E56" s="21" t="n">
         <v>4500000</v>
       </c>
-      <c r="F56" s="40" t="inlineStr">
+      <c r="F56" s="49" t="inlineStr">
         <is>
           <t>IAS 24 Related Party</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="43" t="inlineStr">
+      <c r="A57" s="47" t="inlineStr">
         <is>
           <t>Note 17</t>
         </is>
@@ -24507,14 +24251,14 @@
       <c r="E58" s="21" t="n">
         <v>1000000</v>
       </c>
-      <c r="F58" s="40" t="inlineStr">
+      <c r="F58" s="49" t="inlineStr">
         <is>
           <t>Authorized &amp; Issued</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="43" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>Note 18</t>
         </is>
@@ -24565,14 +24309,14 @@
       <c r="E60" s="21" t="n">
         <v>7961943</v>
       </c>
-      <c r="F60" s="40" t="inlineStr">
+      <c r="F60" s="49" t="inlineStr">
         <is>
           <t>SOCE Roll-Forward</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="43" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>Note 19</t>
         </is>
@@ -24684,10 +24428,10 @@
           <t>NON-CURRENT ASSETS</t>
         </is>
       </c>
-      <c r="B7" s="44" t="n"/>
-      <c r="C7" s="44" t="n"/>
-      <c r="D7" s="44" t="n"/>
-      <c r="E7" s="44" t="n"/>
+      <c r="B7" s="50" t="n"/>
+      <c r="C7" s="50" t="n"/>
+      <c r="D7" s="50" t="n"/>
+      <c r="E7" s="50" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -24706,28 +24450,28 @@
       <c r="D8" s="21" t="n">
         <v>3409540</v>
       </c>
-      <c r="E8" s="40" t="inlineStr">
+      <c r="E8" s="49" t="inlineStr">
         <is>
           <t>IAS 16 Carrying Amount</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="45" t="inlineStr">
+      <c r="A9" s="51" t="inlineStr">
         <is>
           <t>TOTAL NON-CURRENT ASSETS</t>
         </is>
       </c>
-      <c r="B9" s="46" t="n"/>
-      <c r="C9" s="47">
+      <c r="B9" s="52" t="n"/>
+      <c r="C9" s="53">
         <f>C8</f>
         <v/>
       </c>
-      <c r="D9" s="47">
+      <c r="D9" s="53">
         <f>D8</f>
         <v/>
       </c>
-      <c r="E9" s="48" t="inlineStr">
+      <c r="E9" s="54" t="inlineStr">
         <is>
           <t>TIED OUT</t>
         </is>
@@ -24739,10 +24483,10 @@
           <t>CURRENT ASSETS</t>
         </is>
       </c>
-      <c r="B10" s="44" t="n"/>
-      <c r="C10" s="44" t="n"/>
-      <c r="D10" s="44" t="n"/>
-      <c r="E10" s="44" t="n"/>
+      <c r="B10" s="50" t="n"/>
+      <c r="C10" s="50" t="n"/>
+      <c r="D10" s="50" t="n"/>
+      <c r="E10" s="50" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -24761,7 +24505,7 @@
       <c r="D11" s="21" t="n">
         <v>13800000</v>
       </c>
-      <c r="E11" s="40" t="inlineStr">
+      <c r="E11" s="49" t="inlineStr">
         <is>
           <t>IAS 2 Cost / NRV</t>
         </is>
@@ -24784,7 +24528,7 @@
       <c r="D12" s="21" t="n">
         <v>4150000</v>
       </c>
-      <c r="E12" s="40" t="inlineStr">
+      <c r="E12" s="49" t="inlineStr">
         <is>
           <t>IFRS 15 Unbilled Revenue</t>
         </is>
@@ -24807,7 +24551,7 @@
       <c r="D13" s="21" t="n">
         <v>8685000</v>
       </c>
-      <c r="E13" s="40" t="inlineStr">
+      <c r="E13" s="49" t="inlineStr">
         <is>
           <t>IFRS 9 Net of ECL</t>
         </is>
@@ -24830,28 +24574,28 @@
       <c r="D14" s="21" t="n">
         <v>5142678</v>
       </c>
-      <c r="E14" s="40" t="inlineStr">
+      <c r="E14" s="49" t="inlineStr">
         <is>
           <t>Reconciled Bank Balances</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="45" t="inlineStr">
+      <c r="A15" s="51" t="inlineStr">
         <is>
           <t>TOTAL CURRENT ASSETS</t>
         </is>
       </c>
-      <c r="B15" s="46" t="n"/>
-      <c r="C15" s="47">
+      <c r="B15" s="52" t="n"/>
+      <c r="C15" s="53">
         <f>SUM(C11:C14)</f>
         <v/>
       </c>
-      <c r="D15" s="47">
+      <c r="D15" s="53">
         <f>SUM(D11:D14)</f>
         <v/>
       </c>
-      <c r="E15" s="48" t="inlineStr">
+      <c r="E15" s="54" t="inlineStr">
         <is>
           <t>TIED OUT</t>
         </is>
@@ -24884,10 +24628,10 @@
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="B17" s="44" t="n"/>
-      <c r="C17" s="44" t="n"/>
-      <c r="D17" s="44" t="n"/>
-      <c r="E17" s="44" t="n"/>
+      <c r="B17" s="50" t="n"/>
+      <c r="C17" s="50" t="n"/>
+      <c r="D17" s="50" t="n"/>
+      <c r="E17" s="50" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -24906,7 +24650,7 @@
       <c r="D18" s="21" t="n">
         <v>1000000</v>
       </c>
-      <c r="E18" s="40" t="inlineStr">
+      <c r="E18" s="49" t="inlineStr">
         <is>
           <t>1m Ordinary Shares @ ₦1</t>
         </is>
@@ -24929,28 +24673,28 @@
       <c r="D19" s="21" t="n">
         <v>17476718</v>
       </c>
-      <c r="E19" s="40" t="inlineStr">
+      <c r="E19" s="49" t="inlineStr">
         <is>
           <t>Cumulative Post-Tax Earnings</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="45" t="inlineStr">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>TOTAL EQUITY</t>
         </is>
       </c>
-      <c r="B20" s="46" t="n"/>
-      <c r="C20" s="47">
+      <c r="B20" s="52" t="n"/>
+      <c r="C20" s="53">
         <f>SUM(C18:C19)</f>
         <v/>
       </c>
-      <c r="D20" s="47">
+      <c r="D20" s="53">
         <f>SUM(D18:D19)</f>
         <v/>
       </c>
-      <c r="E20" s="48" t="inlineStr">
+      <c r="E20" s="54" t="inlineStr">
         <is>
           <t>TIED OUT</t>
         </is>
@@ -24962,10 +24706,10 @@
           <t>NON-CURRENT LIABILITIES</t>
         </is>
       </c>
-      <c r="B21" s="44" t="n"/>
-      <c r="C21" s="44" t="n"/>
-      <c r="D21" s="44" t="n"/>
-      <c r="E21" s="44" t="n"/>
+      <c r="B21" s="50" t="n"/>
+      <c r="C21" s="50" t="n"/>
+      <c r="D21" s="50" t="n"/>
+      <c r="E21" s="50" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -24984,7 +24728,7 @@
       <c r="D22" s="21" t="n">
         <v>5800000</v>
       </c>
-      <c r="E22" s="40" t="inlineStr">
+      <c r="E22" s="49" t="inlineStr">
         <is>
           <t>IAS 24 Related Party</t>
         </is>
@@ -25007,28 +24751,28 @@
       <c r="D23" s="21" t="n">
         <v>16000</v>
       </c>
-      <c r="E23" s="40" t="inlineStr">
+      <c r="E23" s="49" t="inlineStr">
         <is>
           <t>IAS 12 Temporary Differences</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="45" t="inlineStr">
+      <c r="A24" s="51" t="inlineStr">
         <is>
           <t>TOTAL NON-CURRENT LIABILITIES</t>
         </is>
       </c>
-      <c r="B24" s="46" t="n"/>
-      <c r="C24" s="47">
+      <c r="B24" s="52" t="n"/>
+      <c r="C24" s="53">
         <f>SUM(C22:C23)</f>
         <v/>
       </c>
-      <c r="D24" s="47">
+      <c r="D24" s="53">
         <f>SUM(D22:D23)</f>
         <v/>
       </c>
-      <c r="E24" s="48" t="inlineStr">
+      <c r="E24" s="54" t="inlineStr">
         <is>
           <t>TIED OUT</t>
         </is>
@@ -25040,10 +24784,10 @@
           <t>CURRENT LIABILITIES</t>
         </is>
       </c>
-      <c r="B25" s="44" t="n"/>
-      <c r="C25" s="44" t="n"/>
-      <c r="D25" s="44" t="n"/>
-      <c r="E25" s="44" t="n"/>
+      <c r="B25" s="50" t="n"/>
+      <c r="C25" s="50" t="n"/>
+      <c r="D25" s="50" t="n"/>
+      <c r="E25" s="50" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -25062,7 +24806,7 @@
       <c r="D26" s="21" t="n">
         <v>4825500</v>
       </c>
-      <c r="E26" s="40" t="inlineStr">
+      <c r="E26" s="49" t="inlineStr">
         <is>
           <t>Amortized Cost</t>
         </is>
@@ -25085,7 +24829,7 @@
       <c r="D27" s="21" t="n">
         <v>3600000</v>
       </c>
-      <c r="E27" s="40" t="inlineStr">
+      <c r="E27" s="49" t="inlineStr">
         <is>
           <t>IFRS 15 Customer Advances</t>
         </is>
@@ -25108,28 +24852,28 @@
       <c r="D28" s="21" t="n">
         <v>2469000</v>
       </c>
-      <c r="E28" s="40" t="inlineStr">
+      <c r="E28" s="49" t="inlineStr">
         <is>
           <t>CITA / TETFA Statutory</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="45" t="inlineStr">
+      <c r="A29" s="51" t="inlineStr">
         <is>
           <t>TOTAL CURRENT LIABILITIES</t>
         </is>
       </c>
-      <c r="B29" s="46" t="n"/>
-      <c r="C29" s="47">
+      <c r="B29" s="52" t="n"/>
+      <c r="C29" s="53">
         <f>SUM(C26:C28)</f>
         <v/>
       </c>
-      <c r="D29" s="47">
+      <c r="D29" s="53">
         <f>SUM(D26:D28)</f>
         <v/>
       </c>
-      <c r="E29" s="48" t="inlineStr">
+      <c r="E29" s="54" t="inlineStr">
         <is>
           <t>TIED OUT</t>
         </is>
@@ -25239,21 +24983,21 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="49" t="inlineStr">
+      <c r="A37" s="55" t="inlineStr">
         <is>
           <t>GROSS PROFIT</t>
         </is>
       </c>
-      <c r="B37" s="50" t="n"/>
-      <c r="C37" s="51">
+      <c r="B37" s="56" t="n"/>
+      <c r="C37" s="57">
         <f>SUM(C35:C36)</f>
         <v/>
       </c>
-      <c r="D37" s="51">
+      <c r="D37" s="57">
         <f>SUM(D35:D36)</f>
         <v/>
       </c>
-      <c r="E37" s="52" t="inlineStr">
+      <c r="E37" s="58" t="inlineStr">
         <is>
           <t>Gross Margin: 35.29%</t>
         </is>
@@ -25283,21 +25027,21 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="49" t="inlineStr">
+      <c r="A39" s="55" t="inlineStr">
         <is>
           <t>OPERATING PROFIT (EBIT)</t>
         </is>
       </c>
-      <c r="B39" s="50" t="n"/>
-      <c r="C39" s="51">
+      <c r="B39" s="56" t="n"/>
+      <c r="C39" s="57">
         <f>C37+C38</f>
         <v/>
       </c>
-      <c r="D39" s="51">
+      <c r="D39" s="57">
         <f>D37+D38</f>
         <v/>
       </c>
-      <c r="E39" s="52" t="inlineStr">
+      <c r="E39" s="58" t="inlineStr">
         <is>
           <t>Operating Margin: 20.67%</t>
         </is>
@@ -25327,21 +25071,21 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="49" t="inlineStr">
+      <c r="A41" s="55" t="inlineStr">
         <is>
           <t>PROFIT BEFORE TAXATION</t>
         </is>
       </c>
-      <c r="B41" s="50" t="n"/>
-      <c r="C41" s="51">
+      <c r="B41" s="56" t="n"/>
+      <c r="C41" s="57">
         <f>C39+C40</f>
         <v/>
       </c>
-      <c r="D41" s="51">
+      <c r="D41" s="57">
         <f>D39+D40</f>
         <v/>
       </c>
-      <c r="E41" s="52" t="inlineStr">
+      <c r="E41" s="58" t="inlineStr">
         <is>
           <t>Taxable Accounting Profit</t>
         </is>
@@ -25397,7 +25141,7 @@
           <t>OTHER COMPREHENSIVE INCOME</t>
         </is>
       </c>
-      <c r="B44" s="53" t="n"/>
+      <c r="B44" s="59" t="n"/>
       <c r="C44" s="21" t="n">
         <v>0</v>
       </c>
@@ -25468,15 +25212,15 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="45" t="inlineStr">
+      <c r="A50" s="51" t="inlineStr">
         <is>
           <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
-      <c r="B50" s="46" t="n"/>
-      <c r="C50" s="46" t="n"/>
-      <c r="D50" s="46" t="n"/>
-      <c r="E50" s="54" t="n"/>
+      <c r="B50" s="52" t="n"/>
+      <c r="C50" s="52" t="n"/>
+      <c r="D50" s="52" t="n"/>
+      <c r="E50" s="60" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -25507,9 +25251,9 @@
           <t>Adjustments for non-cash items:</t>
         </is>
       </c>
-      <c r="B52" s="53" t="n"/>
-      <c r="C52" s="53" t="n"/>
-      <c r="D52" s="53" t="n"/>
+      <c r="B52" s="59" t="n"/>
+      <c r="C52" s="59" t="n"/>
+      <c r="D52" s="59" t="n"/>
       <c r="E52" s="7" t="n"/>
     </row>
     <row r="53">
@@ -25587,7 +25331,7 @@
           <t>Operating profit before working capital changes</t>
         </is>
       </c>
-      <c r="B56" s="53" t="n"/>
+      <c r="B56" s="59" t="n"/>
       <c r="C56" s="21">
         <f>SUM(C51:C55)</f>
         <v/>
@@ -25608,9 +25352,9 @@
           <t>Working capital changes:</t>
         </is>
       </c>
-      <c r="B57" s="53" t="n"/>
-      <c r="C57" s="53" t="n"/>
-      <c r="D57" s="53" t="n"/>
+      <c r="B57" s="59" t="n"/>
+      <c r="C57" s="59" t="n"/>
+      <c r="D57" s="59" t="n"/>
       <c r="E57" s="7" t="n"/>
     </row>
     <row r="58">
@@ -25734,7 +25478,7 @@
           <t>Cash generated from operations</t>
         </is>
       </c>
-      <c r="B63" s="53" t="n"/>
+      <c r="B63" s="59" t="n"/>
       <c r="C63" s="21">
         <f>C56+SUM(C58:C62)</f>
         <v/>
@@ -25801,7 +25545,7 @@
           <t>Net cash flows from operating activities</t>
         </is>
       </c>
-      <c r="B66" s="44" t="n"/>
+      <c r="B66" s="50" t="n"/>
       <c r="C66" s="17">
         <f>C63+C64+C65</f>
         <v/>
@@ -25817,15 +25561,15 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="45" t="inlineStr">
+      <c r="A67" s="51" t="inlineStr">
         <is>
           <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
-      <c r="B67" s="46" t="n"/>
-      <c r="C67" s="46" t="n"/>
-      <c r="D67" s="46" t="n"/>
-      <c r="E67" s="54" t="n"/>
+      <c r="B67" s="52" t="n"/>
+      <c r="C67" s="52" t="n"/>
+      <c r="D67" s="52" t="n"/>
+      <c r="E67" s="60" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -25856,7 +25600,7 @@
           <t>Net cash flows used in investing activities</t>
         </is>
       </c>
-      <c r="B69" s="44" t="n"/>
+      <c r="B69" s="50" t="n"/>
       <c r="C69" s="17">
         <f>C68</f>
         <v/>
@@ -25872,15 +25616,15 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="45" t="inlineStr">
+      <c r="A70" s="51" t="inlineStr">
         <is>
           <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
-      <c r="B70" s="46" t="n"/>
-      <c r="C70" s="46" t="n"/>
-      <c r="D70" s="46" t="n"/>
-      <c r="E70" s="54" t="n"/>
+      <c r="B70" s="52" t="n"/>
+      <c r="C70" s="52" t="n"/>
+      <c r="D70" s="52" t="n"/>
+      <c r="E70" s="60" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -25911,7 +25655,7 @@
           <t>Net cash flows from financing activities</t>
         </is>
       </c>
-      <c r="B72" s="44" t="n"/>
+      <c r="B72" s="50" t="n"/>
       <c r="C72" s="17">
         <f>C71</f>
         <v/>
@@ -25932,7 +25676,7 @@
           <t>Net increase in cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B73" s="53" t="n"/>
+      <c r="B73" s="59" t="n"/>
       <c r="C73" s="21">
         <f>C66+C69+C72</f>
         <v/>
@@ -25976,7 +25720,7 @@
           <t>CASH AND CASH EQUIVALENTS AT 31 DECEMBER</t>
         </is>
       </c>
-      <c r="B75" s="37" t="inlineStr">
+      <c r="B75" s="45" t="inlineStr">
         <is>
           <t>Note 11</t>
         </is>
@@ -25989,7 +25733,7 @@
         <f>D73+D74</f>
         <v/>
       </c>
-      <c r="E75" s="55" t="inlineStr">
+      <c r="E75" s="61" t="inlineStr">
         <is>
           <t>TIED TO SFP NOTE 11</t>
         </is>
@@ -26080,9 +25824,9 @@
           <t>Corporate Profile, RC 1526224, Registered in Nigeria under CAMA</t>
         </is>
       </c>
-      <c r="D5" s="44" t="n"/>
-      <c r="E5" s="44" t="n"/>
-      <c r="F5" s="41" t="inlineStr">
+      <c r="D5" s="50" t="n"/>
+      <c r="E5" s="50" t="n"/>
+      <c r="F5" s="48" t="inlineStr">
         <is>
           <t>IAS 1.51</t>
         </is>
@@ -26104,9 +25848,9 @@
           <t>Compliance with full IFRS, FRCN &amp; historical cost convention</t>
         </is>
       </c>
-      <c r="D6" s="53" t="n"/>
-      <c r="E6" s="53" t="n"/>
-      <c r="F6" s="40" t="inlineStr">
+      <c r="D6" s="59" t="n"/>
+      <c r="E6" s="59" t="n"/>
+      <c r="F6" s="49" t="inlineStr">
         <is>
           <t>IAS 1.112</t>
         </is>
@@ -26134,7 +25878,7 @@
       <c r="E7" s="22" t="n">
         <v>38000000</v>
       </c>
-      <c r="F7" s="41" t="inlineStr">
+      <c r="F7" s="48" t="inlineStr">
         <is>
           <t>IFRS 15 Over Time</t>
         </is>
@@ -26162,7 +25906,7 @@
       <c r="E8" s="21" t="n">
         <v>19500000</v>
       </c>
-      <c r="F8" s="40" t="inlineStr">
+      <c r="F8" s="49" t="inlineStr">
         <is>
           <t>IFRS 15 Point in Time</t>
         </is>
@@ -26190,14 +25934,14 @@
       <c r="E9" s="22" t="n">
         <v>6700000</v>
       </c>
-      <c r="F9" s="41" t="inlineStr">
+      <c r="F9" s="48" t="inlineStr">
         <is>
           <t>IFRS 15 Over Time</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>Note 3</t>
         </is>
@@ -26248,7 +25992,7 @@
       <c r="E11" s="22" t="n">
         <v>26400000</v>
       </c>
-      <c r="F11" s="41" t="inlineStr">
+      <c r="F11" s="48" t="inlineStr">
         <is>
           <t>IAS 2 Direct Materials</t>
         </is>
@@ -26276,7 +26020,7 @@
       <c r="E12" s="21" t="n">
         <v>11800000</v>
       </c>
-      <c r="F12" s="40" t="inlineStr">
+      <c r="F12" s="49" t="inlineStr">
         <is>
           <t>IAS 2 Inventory Cost</t>
         </is>
@@ -26304,14 +26048,14 @@
       <c r="E13" s="22" t="n">
         <v>3300000</v>
       </c>
-      <c r="F13" s="41" t="inlineStr">
+      <c r="F13" s="48" t="inlineStr">
         <is>
           <t>IAS 2 Direct Labor</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="47" t="inlineStr">
         <is>
           <t>Note 4</t>
         </is>
@@ -26362,7 +26106,7 @@
       <c r="E15" s="22" t="n">
         <v>4200000</v>
       </c>
-      <c r="F15" s="41" t="inlineStr">
+      <c r="F15" s="48" t="inlineStr">
         <is>
           <t>IAS 19 Employee Costs</t>
         </is>
@@ -26390,7 +26134,7 @@
       <c r="E16" s="21" t="n">
         <v>1450000</v>
       </c>
-      <c r="F16" s="40" t="inlineStr">
+      <c r="F16" s="49" t="inlineStr">
         <is>
           <t>Operating Overheads</t>
         </is>
@@ -26418,7 +26162,7 @@
       <c r="E17" s="22" t="n">
         <v>980000</v>
       </c>
-      <c r="F17" s="41" t="inlineStr">
+      <c r="F17" s="48" t="inlineStr">
         <is>
           <t>Professional Services</t>
         </is>
@@ -26446,7 +26190,7 @@
       <c r="E18" s="21" t="n">
         <v>450000</v>
       </c>
-      <c r="F18" s="40" t="inlineStr">
+      <c r="F18" s="49" t="inlineStr">
         <is>
           <t>Audit Fees Accrual</t>
         </is>
@@ -26474,7 +26218,7 @@
       <c r="E19" s="22" t="n">
         <v>420000</v>
       </c>
-      <c r="F19" s="41" t="inlineStr">
+      <c r="F19" s="48" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -26502,7 +26246,7 @@
       <c r="E20" s="21" t="n">
         <v>750000</v>
       </c>
-      <c r="F20" s="40" t="inlineStr">
+      <c r="F20" s="49" t="inlineStr">
         <is>
           <t>Transport &amp; Travel</t>
         </is>
@@ -26530,7 +26274,7 @@
       <c r="E21" s="22" t="n">
         <v>715000</v>
       </c>
-      <c r="F21" s="41" t="inlineStr">
+      <c r="F21" s="48" t="inlineStr">
         <is>
           <t>IAS 16 Depreciation</t>
         </is>
@@ -26558,7 +26302,7 @@
       <c r="E22" s="21" t="n">
         <v>260000</v>
       </c>
-      <c r="F22" s="40" t="inlineStr">
+      <c r="F22" s="49" t="inlineStr">
         <is>
           <t>IFRS 9 Impairment</t>
         </is>
@@ -26586,14 +26330,14 @@
       <c r="E23" s="22" t="n">
         <v>625000</v>
       </c>
-      <c r="F23" s="41" t="inlineStr">
+      <c r="F23" s="48" t="inlineStr">
         <is>
           <t>General Administration</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="43" t="inlineStr">
+      <c r="A24" s="47" t="inlineStr">
         <is>
           <t>Note 5</t>
         </is>
@@ -26644,14 +26388,14 @@
       <c r="E25" s="22" t="n">
         <v>350000</v>
       </c>
-      <c r="F25" s="41" t="inlineStr">
+      <c r="F25" s="48" t="inlineStr">
         <is>
           <t>IAS 23 Borrowing Costs</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="43" t="inlineStr">
+      <c r="A26" s="47" t="inlineStr">
         <is>
           <t>Note 6</t>
         </is>
@@ -26702,7 +26446,7 @@
       <c r="E27" s="22" t="n">
         <v>1047040</v>
       </c>
-      <c r="F27" s="41" t="inlineStr">
+      <c r="F27" s="48" t="inlineStr">
         <is>
           <t>IAS 16 Carrying Amount</t>
         </is>
@@ -26730,7 +26474,7 @@
       <c r="E28" s="21" t="n">
         <v>2362500</v>
       </c>
-      <c r="F28" s="40" t="inlineStr">
+      <c r="F28" s="49" t="inlineStr">
         <is>
           <t>IAS 16 Carrying Amount</t>
         </is>
@@ -26758,14 +26502,14 @@
       <c r="E29" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F29" s="41" t="inlineStr">
+      <c r="F29" s="48" t="inlineStr">
         <is>
           <t>IAS 16 Carrying Amount</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="43" t="inlineStr">
+      <c r="A30" s="47" t="inlineStr">
         <is>
           <t>Note 7</t>
         </is>
@@ -26816,7 +26560,7 @@
       <c r="E31" s="22" t="n">
         <v>8200000</v>
       </c>
-      <c r="F31" s="41" t="inlineStr">
+      <c r="F31" s="48" t="inlineStr">
         <is>
           <t>IAS 2 Lower of Cost/NRV</t>
         </is>
@@ -26844,14 +26588,14 @@
       <c r="E32" s="21" t="n">
         <v>5600000</v>
       </c>
-      <c r="F32" s="40" t="inlineStr">
+      <c r="F32" s="49" t="inlineStr">
         <is>
           <t>IAS 2 Lower of Cost/NRV</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="43" t="inlineStr">
+      <c r="A33" s="47" t="inlineStr">
         <is>
           <t>Note 8</t>
         </is>
@@ -26902,14 +26646,14 @@
       <c r="E34" s="21" t="n">
         <v>4150000</v>
       </c>
-      <c r="F34" s="40" t="inlineStr">
+      <c r="F34" s="49" t="inlineStr">
         <is>
           <t>IFRS 15 Unbilled Asset</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="43" t="inlineStr">
+      <c r="A35" s="47" t="inlineStr">
         <is>
           <t>Note 9</t>
         </is>
@@ -26960,7 +26704,7 @@
       <c r="E36" s="21" t="n">
         <v>5800000</v>
       </c>
-      <c r="F36" s="40" t="inlineStr">
+      <c r="F36" s="49" t="inlineStr">
         <is>
           <t>Amortized Cost</t>
         </is>
@@ -26988,7 +26732,7 @@
       <c r="E37" s="22" t="n">
         <v>-445000</v>
       </c>
-      <c r="F37" s="41" t="inlineStr">
+      <c r="F37" s="48" t="inlineStr">
         <is>
           <t>IFRS 9 ECL Provision</t>
         </is>
@@ -27016,7 +26760,7 @@
       <c r="E38" s="21" t="n">
         <v>2650000</v>
       </c>
-      <c r="F38" s="40" t="inlineStr">
+      <c r="F38" s="49" t="inlineStr">
         <is>
           <t>FIRS Credit Notes</t>
         </is>
@@ -27044,14 +26788,14 @@
       <c r="E39" s="22" t="n">
         <v>680000</v>
       </c>
-      <c r="F39" s="41" t="inlineStr">
+      <c r="F39" s="48" t="inlineStr">
         <is>
           <t>Operating Prepayments</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="43" t="inlineStr">
+      <c r="A40" s="47" t="inlineStr">
         <is>
           <t>Note 10</t>
         </is>
@@ -27102,7 +26846,7 @@
       <c r="E41" s="22" t="n">
         <v>3850210</v>
       </c>
-      <c r="F41" s="41" t="inlineStr">
+      <c r="F41" s="48" t="inlineStr">
         <is>
           <t>Primary Operating A/C</t>
         </is>
@@ -27130,7 +26874,7 @@
       <c r="E42" s="21" t="n">
         <v>980118</v>
       </c>
-      <c r="F42" s="40" t="inlineStr">
+      <c r="F42" s="49" t="inlineStr">
         <is>
           <t>Site Collection A/C</t>
         </is>
@@ -27158,14 +26902,14 @@
       <c r="E43" s="22" t="n">
         <v>312350</v>
       </c>
-      <c r="F43" s="41" t="inlineStr">
+      <c r="F43" s="48" t="inlineStr">
         <is>
           <t>Disbursement A/C</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="43" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>Note 11</t>
         </is>
@@ -27216,14 +26960,14 @@
       <c r="E45" s="22" t="n">
         <v>3600000</v>
       </c>
-      <c r="F45" s="41" t="inlineStr">
+      <c r="F45" s="48" t="inlineStr">
         <is>
           <t>IFRS 15 Advances</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="43" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>Note 13</t>
         </is>
@@ -27274,7 +27018,7 @@
       <c r="E47" s="22" t="n">
         <v>3850000</v>
       </c>
-      <c r="F47" s="41" t="inlineStr">
+      <c r="F47" s="48" t="inlineStr">
         <is>
           <t>Trade Creditors</t>
         </is>
@@ -27302,7 +27046,7 @@
       <c r="E48" s="21" t="n">
         <v>550000</v>
       </c>
-      <c r="F48" s="40" t="inlineStr">
+      <c r="F48" s="49" t="inlineStr">
         <is>
           <t>Audit Accrual</t>
         </is>
@@ -27330,14 +27074,14 @@
       <c r="E49" s="22" t="n">
         <v>425500</v>
       </c>
-      <c r="F49" s="41" t="inlineStr">
+      <c r="F49" s="48" t="inlineStr">
         <is>
           <t>Sundry Accruals</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="43" t="inlineStr">
+      <c r="A50" s="47" t="inlineStr">
         <is>
           <t>Note 14</t>
         </is>
@@ -27388,14 +27132,14 @@
       <c r="E51" s="22" t="n">
         <v>-16000</v>
       </c>
-      <c r="F51" s="41" t="inlineStr">
+      <c r="F51" s="48" t="inlineStr">
         <is>
           <t>IAS 12 Net Liability</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="43" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>Note 15</t>
         </is>
@@ -27446,7 +27190,7 @@
       <c r="E53" s="22" t="n">
         <v>2528000</v>
       </c>
-      <c r="F53" s="41" t="inlineStr">
+      <c r="F53" s="48" t="inlineStr">
         <is>
           <t>30% CIT Large Co</t>
         </is>
@@ -27474,7 +27218,7 @@
       <c r="E54" s="21" t="n">
         <v>408600</v>
       </c>
-      <c r="F54" s="40" t="inlineStr">
+      <c r="F54" s="49" t="inlineStr">
         <is>
           <t>3% TETFA Rate</t>
         </is>
@@ -27502,7 +27246,7 @@
       <c r="E55" s="22" t="n">
         <v>625</v>
       </c>
-      <c r="F55" s="41" t="inlineStr">
+      <c r="F55" s="48" t="inlineStr">
         <is>
           <t>0.005% of PBT</t>
         </is>
@@ -27530,14 +27274,14 @@
       <c r="E56" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F56" s="40" t="inlineStr">
+      <c r="F56" s="49" t="inlineStr">
         <is>
           <t>0.25% of PBT</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="43" t="inlineStr">
+      <c r="A57" s="47" t="inlineStr">
         <is>
           <t>Note 16</t>
         </is>
@@ -27588,14 +27332,14 @@
       <c r="E58" s="21" t="n">
         <v>5800000</v>
       </c>
-      <c r="F58" s="40" t="inlineStr">
+      <c r="F58" s="49" t="inlineStr">
         <is>
           <t>IAS 24 Related Party</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="43" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>Note 17</t>
         </is>
@@ -27646,14 +27390,14 @@
       <c r="E60" s="21" t="n">
         <v>1000000</v>
       </c>
-      <c r="F60" s="40" t="inlineStr">
+      <c r="F60" s="49" t="inlineStr">
         <is>
           <t>Authorized &amp; Issued</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="43" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>Note 18</t>
         </is>
@@ -27704,14 +27448,14 @@
       <c r="E62" s="21" t="n">
         <v>17476718</v>
       </c>
-      <c r="F62" s="40" t="inlineStr">
+      <c r="F62" s="49" t="inlineStr">
         <is>
           <t>SOCE Roll-Forward</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="43" t="inlineStr">
+      <c r="A63" s="47" t="inlineStr">
         <is>
           <t>Note 19</t>
         </is>
@@ -27816,17 +27560,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="56" t="inlineStr">
+      <c r="A5" s="62" t="inlineStr">
         <is>
           <t>STATEMENT OF PROFIT OR LOSS SUMMARY</t>
         </is>
       </c>
-      <c r="B5" s="57" t="n"/>
-      <c r="C5" s="57" t="n"/>
-      <c r="D5" s="57" t="n"/>
-      <c r="E5" s="57" t="n"/>
-      <c r="F5" s="57" t="n"/>
-      <c r="G5" s="58" t="n"/>
+      <c r="B5" s="63" t="n"/>
+      <c r="C5" s="63" t="n"/>
+      <c r="D5" s="63" t="n"/>
+      <c r="E5" s="63" t="n"/>
+      <c r="F5" s="63" t="n"/>
+      <c r="G5" s="64" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -27846,7 +27590,7 @@
       <c r="E6" s="21" t="n">
         <v>112500000</v>
       </c>
-      <c r="F6" s="59" t="n">
+      <c r="F6" s="65" t="n">
         <v>1.365</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -27873,7 +27617,7 @@
       <c r="E7" s="22" t="n">
         <v>-72800000</v>
       </c>
-      <c r="F7" s="60" t="n">
+      <c r="F7" s="66" t="n">
         <v>1.411</v>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -27900,7 +27644,7 @@
       <c r="E8" s="24" t="n">
         <v>39700000</v>
       </c>
-      <c r="F8" s="61" t="n">
+      <c r="F8" s="67" t="n">
         <v>1.292</v>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -27927,7 +27671,7 @@
       <c r="E9" s="22" t="n">
         <v>-16450000</v>
       </c>
-      <c r="F9" s="60" t="n">
+      <c r="F9" s="66" t="n">
         <v>0.852</v>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -27954,7 +27698,7 @@
       <c r="E10" s="24" t="n">
         <v>23250000</v>
       </c>
-      <c r="F10" s="61" t="n">
+      <c r="F10" s="67" t="n">
         <v>2.197</v>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -27981,7 +27725,7 @@
       <c r="E11" s="22" t="n">
         <v>-650000</v>
       </c>
-      <c r="F11" s="44" t="n"/>
+      <c r="F11" s="50" t="n"/>
       <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Commercial bank project facility interest</t>
@@ -28006,7 +27750,7 @@
       <c r="E12" s="21" t="n">
         <v>22600000</v>
       </c>
-      <c r="F12" s="59" t="n">
+      <c r="F12" s="65" t="n">
         <v>2.166</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -28033,7 +27777,7 @@
       <c r="E13" s="22" t="n">
         <v>-7700130</v>
       </c>
-      <c r="F13" s="44" t="n"/>
+      <c r="F13" s="50" t="n"/>
       <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Current tax + IAS 12 deferred tax charges</t>
@@ -28058,7 +27802,7 @@
       <c r="E14" s="24" t="n">
         <v>14899870</v>
       </c>
-      <c r="F14" s="61" t="n">
+      <c r="F14" s="67" t="n">
         <v>1.756</v>
       </c>
       <c r="G14" s="25" t="inlineStr">
@@ -28068,17 +27812,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="56" t="inlineStr">
+      <c r="A15" s="62" t="inlineStr">
         <is>
           <t>STATEMENT OF FINANCIAL POSITION SUMMARY</t>
         </is>
       </c>
-      <c r="B15" s="57" t="n"/>
-      <c r="C15" s="57" t="n"/>
-      <c r="D15" s="57" t="n"/>
-      <c r="E15" s="57" t="n"/>
-      <c r="F15" s="57" t="n"/>
-      <c r="G15" s="58" t="n"/>
+      <c r="B15" s="63" t="n"/>
+      <c r="C15" s="63" t="n"/>
+      <c r="D15" s="63" t="n"/>
+      <c r="E15" s="63" t="n"/>
+      <c r="F15" s="63" t="n"/>
+      <c r="G15" s="64" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -28098,7 +27842,7 @@
       <c r="E16" s="21" t="n">
         <v>5724540</v>
       </c>
-      <c r="F16" s="59" t="n">
+      <c r="F16" s="65" t="n">
         <v>7.371</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
@@ -28125,7 +27869,7 @@
       <c r="E17" s="22" t="n">
         <v>24300000</v>
       </c>
-      <c r="F17" s="44" t="n"/>
+      <c r="F17" s="50" t="n"/>
       <c r="G17" s="10" t="inlineStr">
         <is>
           <t>IAS 2 land bank &amp; civil construction WIP</t>
@@ -28150,7 +27894,7 @@
       <c r="E18" s="21" t="n">
         <v>6850000</v>
       </c>
-      <c r="F18" s="53" t="n"/>
+      <c r="F18" s="59" t="n"/>
       <c r="G18" s="7" t="inlineStr">
         <is>
           <t>IFRS 15 unbilled certified progress billings</t>
@@ -28175,7 +27919,7 @@
       <c r="E19" s="22" t="n">
         <v>14360000</v>
       </c>
-      <c r="F19" s="60" t="n">
+      <c r="F19" s="66" t="n">
         <v>0.621</v>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -28202,7 +27946,7 @@
       <c r="E20" s="21" t="n">
         <v>8924048</v>
       </c>
-      <c r="F20" s="59" t="n">
+      <c r="F20" s="65" t="n">
         <v>4.54</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
@@ -28229,7 +27973,7 @@
       <c r="E21" s="24" t="n">
         <v>60158588</v>
       </c>
-      <c r="F21" s="61" t="n">
+      <c r="F21" s="67" t="n">
         <v>1.597</v>
       </c>
       <c r="G21" s="25" t="inlineStr">
@@ -28256,7 +28000,7 @@
       <c r="E22" s="21" t="n">
         <v>1000000</v>
       </c>
-      <c r="F22" s="59" t="n">
+      <c r="F22" s="65" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
@@ -28283,7 +28027,7 @@
       <c r="E23" s="22" t="n">
         <v>32376588</v>
       </c>
-      <c r="F23" s="60" t="n">
+      <c r="F23" s="66" t="n">
         <v>1.393</v>
       </c>
       <c r="G23" s="10" t="inlineStr">
@@ -28310,7 +28054,7 @@
       <c r="E24" s="24" t="n">
         <v>33376588</v>
       </c>
-      <c r="F24" s="61" t="n">
+      <c r="F24" s="67" t="n">
         <v>1.149</v>
       </c>
       <c r="G24" s="25" t="inlineStr">
@@ -28337,7 +28081,7 @@
       <c r="E25" s="22" t="n">
         <v>7500000</v>
       </c>
-      <c r="F25" s="44" t="n"/>
+      <c r="F25" s="50" t="n"/>
       <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Managing Director long-term project loans</t>
@@ -28362,7 +28106,7 @@
       <c r="E26" s="21" t="n">
         <v>19183500</v>
       </c>
-      <c r="F26" s="59" t="n">
+      <c r="F26" s="65" t="n">
         <v>5.372</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -28372,17 +28116,17 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="56" t="inlineStr">
+      <c r="A27" s="62" t="inlineStr">
         <is>
           <t>KEY FINANCIAL &amp; PERFORMANCE RATIOS</t>
         </is>
       </c>
-      <c r="B27" s="57" t="n"/>
-      <c r="C27" s="57" t="n"/>
-      <c r="D27" s="57" t="n"/>
-      <c r="E27" s="57" t="n"/>
-      <c r="F27" s="57" t="n"/>
-      <c r="G27" s="58" t="n"/>
+      <c r="B27" s="63" t="n"/>
+      <c r="C27" s="63" t="n"/>
+      <c r="D27" s="63" t="n"/>
+      <c r="E27" s="63" t="n"/>
+      <c r="F27" s="63" t="n"/>
+      <c r="G27" s="64" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -28390,19 +28134,19 @@
           <t>Gross Profit Margin (%)</t>
         </is>
       </c>
-      <c r="B28" s="62" t="n">
+      <c r="B28" s="68" t="n">
         <v>0.3882</v>
       </c>
-      <c r="C28" s="62" t="n">
+      <c r="C28" s="68" t="n">
         <v>0.3597</v>
       </c>
-      <c r="D28" s="62" t="n">
+      <c r="D28" s="68" t="n">
         <v>0.3536</v>
       </c>
-      <c r="E28" s="62" t="n">
+      <c r="E28" s="68" t="n">
         <v>0.3529</v>
       </c>
-      <c r="F28" s="53" t="n"/>
+      <c r="F28" s="59" t="n"/>
       <c r="G28" s="7" t="inlineStr">
         <is>
           <t>Stable 35.3% - 36.0% project gross margins</t>
@@ -28415,19 +28159,19 @@
           <t>Operating Profit Margin (%)</t>
         </is>
       </c>
-      <c r="B29" s="63" t="n">
+      <c r="B29" s="69" t="n">
         <v>0.0837</v>
       </c>
-      <c r="C29" s="63" t="n">
+      <c r="C29" s="69" t="n">
         <v>0.1929</v>
       </c>
-      <c r="D29" s="63" t="n">
+      <c r="D29" s="69" t="n">
         <v>0.2002</v>
       </c>
-      <c r="E29" s="63" t="n">
+      <c r="E29" s="69" t="n">
         <v>0.2067</v>
       </c>
-      <c r="F29" s="44" t="n"/>
+      <c r="F29" s="50" t="n"/>
       <c r="G29" s="10" t="inlineStr">
         <is>
           <t>Operating margin expanded above 20.6%</t>
@@ -28440,19 +28184,19 @@
           <t>Net Profit Margin (%)</t>
         </is>
       </c>
-      <c r="B30" s="62" t="n">
+      <c r="B30" s="68" t="n">
         <v>0.0837</v>
       </c>
-      <c r="C30" s="62" t="n">
+      <c r="C30" s="68" t="n">
         <v>0.1455</v>
       </c>
-      <c r="D30" s="62" t="n">
+      <c r="D30" s="68" t="n">
         <v>0.1482</v>
       </c>
-      <c r="E30" s="62" t="n">
+      <c r="E30" s="68" t="n">
         <v>0.1324</v>
       </c>
-      <c r="F30" s="53" t="n"/>
+      <c r="F30" s="59" t="n"/>
       <c r="G30" s="7" t="inlineStr">
         <is>
           <t>Solid net earnings margin after 30% large CIT</t>
@@ -28465,19 +28209,19 @@
           <t>Current Ratio (Times)</t>
         </is>
       </c>
-      <c r="B31" s="64" t="n">
+      <c r="B31" s="70" t="n">
         <v>45.7</v>
       </c>
-      <c r="C31" s="64" t="n">
+      <c r="C31" s="70" t="n">
         <v>2.74</v>
       </c>
-      <c r="D31" s="64" t="n">
+      <c r="D31" s="70" t="n">
         <v>2.92</v>
       </c>
-      <c r="E31" s="64" t="n">
+      <c r="E31" s="70" t="n">
         <v>2.84</v>
       </c>
-      <c r="F31" s="44" t="n"/>
+      <c r="F31" s="50" t="n"/>
       <c r="G31" s="10" t="inlineStr">
         <is>
           <t>Healthy liquidity covering current debt &gt;2.8x</t>
@@ -28490,19 +28234,19 @@
           <t>Return on Equity (ROE %)</t>
         </is>
       </c>
-      <c r="B32" s="62" t="n">
+      <c r="B32" s="68" t="n">
         <v>0.2117</v>
       </c>
-      <c r="C32" s="62" t="n">
+      <c r="C32" s="68" t="n">
         <v>0.6249</v>
       </c>
-      <c r="D32" s="62" t="n">
+      <c r="D32" s="68" t="n">
         <v>0.5149</v>
       </c>
-      <c r="E32" s="62" t="n">
+      <c r="E32" s="68" t="n">
         <v>0.4464</v>
       </c>
-      <c r="F32" s="53" t="n"/>
+      <c r="F32" s="59" t="n"/>
       <c r="G32" s="7" t="inlineStr">
         <is>
           <t>Exceptional capital efficiency and equity return</t>
@@ -28515,19 +28259,19 @@
           <t>Return on Assets (ROA %)</t>
         </is>
       </c>
-      <c r="B33" s="63" t="n">
+      <c r="B33" s="69" t="n">
         <v>0.2071</v>
       </c>
-      <c r="C33" s="63" t="n">
+      <c r="C33" s="69" t="n">
         <v>0.275</v>
       </c>
-      <c r="D33" s="63" t="n">
+      <c r="D33" s="69" t="n">
         <v>0.2704</v>
       </c>
-      <c r="E33" s="63" t="n">
+      <c r="E33" s="69" t="n">
         <v>0.2477</v>
       </c>
-      <c r="F33" s="44" t="n"/>
+      <c r="F33" s="50" t="n"/>
       <c r="G33" s="10" t="inlineStr">
         <is>
           <t>Robust operating asset productivity &gt;24.8%</t>
@@ -28630,7 +28374,7 @@
       <c r="F5" s="22" t="n">
         <v>-8650000</v>
       </c>
-      <c r="G5" s="41" t="inlineStr">
+      <c r="G5" s="48" t="inlineStr">
         <is>
           <t>Cash Outflow: Capitalized Land &amp; WIP</t>
         </is>
@@ -28657,7 +28401,7 @@
       <c r="F6" s="21" t="n">
         <v>-2400000</v>
       </c>
-      <c r="G6" s="40" t="inlineStr">
+      <c r="G6" s="49" t="inlineStr">
         <is>
           <t>Cash Outflow: Unbilled Certified Revenue</t>
         </is>
@@ -28684,7 +28428,7 @@
       <c r="F7" s="22" t="n">
         <v>-1825332</v>
       </c>
-      <c r="G7" s="41" t="inlineStr">
+      <c r="G7" s="48" t="inlineStr">
         <is>
           <t>Cash Outflow: Net Customer Billings Pending</t>
         </is>
@@ -28711,7 +28455,7 @@
       <c r="F8" s="21" t="n">
         <v>2695235</v>
       </c>
-      <c r="G8" s="40" t="inlineStr">
+      <c r="G8" s="49" t="inlineStr">
         <is>
           <t>Cash Inflow: Supplier &amp; Accrual Financing</t>
         </is>
@@ -28738,7 +28482,7 @@
       <c r="F9" s="22" t="n">
         <v>2400000</v>
       </c>
-      <c r="G9" s="41" t="inlineStr">
+      <c r="G9" s="48" t="inlineStr">
         <is>
           <t>Cash Inflow: Off-Plan Customer Deposits</t>
         </is>
@@ -28784,7 +28528,7 @@
       <c r="F11" s="22" t="n">
         <v>-5150000</v>
       </c>
-      <c r="G11" s="41" t="inlineStr">
+      <c r="G11" s="48" t="inlineStr">
         <is>
           <t>Cash Outflow: Capitalized Land &amp; WIP</t>
         </is>
@@ -28811,7 +28555,7 @@
       <c r="F12" s="21" t="n">
         <v>-1750000</v>
       </c>
-      <c r="G12" s="40" t="inlineStr">
+      <c r="G12" s="49" t="inlineStr">
         <is>
           <t>Cash Outflow: Unbilled Certified Revenue</t>
         </is>
@@ -28838,7 +28582,7 @@
       <c r="F13" s="22" t="n">
         <v>-3930000</v>
       </c>
-      <c r="G13" s="41" t="inlineStr">
+      <c r="G13" s="48" t="inlineStr">
         <is>
           <t>Cash Outflow: Net Customer Billings Pending</t>
         </is>
@@ -28865,7 +28609,7 @@
       <c r="F14" s="21" t="n">
         <v>2055265</v>
       </c>
-      <c r="G14" s="40" t="inlineStr">
+      <c r="G14" s="49" t="inlineStr">
         <is>
           <t>Cash Inflow: Supplier &amp; Accrual Financing</t>
         </is>
@@ -28892,7 +28636,7 @@
       <c r="F15" s="22" t="n">
         <v>1200000</v>
       </c>
-      <c r="G15" s="41" t="inlineStr">
+      <c r="G15" s="48" t="inlineStr">
         <is>
           <t>Cash Inflow: Off-Plan Customer Deposits</t>
         </is>
@@ -28938,7 +28682,7 @@
       <c r="F17" s="22" t="n">
         <v>-10500000</v>
       </c>
-      <c r="G17" s="41" t="inlineStr">
+      <c r="G17" s="48" t="inlineStr">
         <is>
           <t>Cash Outflow: Capitalized Land &amp; WIP</t>
         </is>
@@ -28965,7 +28709,7 @@
       <c r="F18" s="21" t="n">
         <v>-2700000</v>
       </c>
-      <c r="G18" s="40" t="inlineStr">
+      <c r="G18" s="49" t="inlineStr">
         <is>
           <t>Cash Outflow: Unbilled Certified Revenue</t>
         </is>
@@ -28992,7 +28736,7 @@
       <c r="F19" s="22" t="n">
         <v>-6070000</v>
       </c>
-      <c r="G19" s="41" t="inlineStr">
+      <c r="G19" s="48" t="inlineStr">
         <is>
           <t>Cash Outflow: Net Customer Billings Pending</t>
         </is>
@@ -29019,7 +28763,7 @@
       <c r="F20" s="21" t="n">
         <v>3158000</v>
       </c>
-      <c r="G20" s="40" t="inlineStr">
+      <c r="G20" s="49" t="inlineStr">
         <is>
           <t>Cash Inflow: Supplier &amp; Accrual Financing</t>
         </is>
@@ -29046,7 +28790,7 @@
       <c r="F21" s="22" t="n">
         <v>2200000</v>
       </c>
-      <c r="G21" s="41" t="inlineStr">
+      <c r="G21" s="48" t="inlineStr">
         <is>
           <t>Cash Inflow: Off-Plan Customer Deposits</t>
         </is>
@@ -29478,7 +29222,7 @@
         <f>IF(F5&lt;=0.01, "PASSED (100%)", "FAILED")</f>
         <v/>
       </c>
-      <c r="I5" s="65" t="inlineStr">
+      <c r="I5" s="71" t="inlineStr">
         <is>
           <t>PASSED (100%)</t>
         </is>
@@ -29524,7 +29268,7 @@
         <f>IF(F6&lt;=0.01, "PASSED (100%)", "FAILED")</f>
         <v/>
       </c>
-      <c r="I6" s="65" t="inlineStr">
+      <c r="I6" s="71" t="inlineStr">
         <is>
           <t>PASSED (100%)</t>
         </is>
@@ -29570,7 +29314,7 @@
         <f>IF(F7&lt;=0.01, "PASSED (100%)", "FAILED")</f>
         <v/>
       </c>
-      <c r="I7" s="65" t="inlineStr">
+      <c r="I7" s="71" t="inlineStr">
         <is>
           <t>PASSED (100%)</t>
         </is>
@@ -29616,7 +29360,7 @@
         <f>IF(F8&lt;=0.01, "PASSED (100%)", "FAILED")</f>
         <v/>
       </c>
-      <c r="I8" s="65" t="inlineStr">
+      <c r="I8" s="71" t="inlineStr">
         <is>
           <t>PASSED (100%)</t>
         </is>
@@ -29662,7 +29406,7 @@
         <f>IF(F9&lt;=0.01, "PASSED (100%)", "FAILED")</f>
         <v/>
       </c>
-      <c r="I9" s="65" t="inlineStr">
+      <c r="I9" s="71" t="inlineStr">
         <is>
           <t>PASSED (100%)</t>
         </is>
@@ -29708,7 +29452,7 @@
         <f>IF(F10&lt;=0.01, "PASSED (100%)", "FAILED")</f>
         <v/>
       </c>
-      <c r="I10" s="65" t="inlineStr">
+      <c r="I10" s="71" t="inlineStr">
         <is>
           <t>PASSED (100%)</t>
         </is>
@@ -29754,7 +29498,7 @@
         <f>IF(F11&lt;=0.01, "PASSED (100%)", "FAILED")</f>
         <v/>
       </c>
-      <c r="I11" s="65" t="inlineStr">
+      <c r="I11" s="71" t="inlineStr">
         <is>
           <t>PASSED (100%)</t>
         </is>
@@ -29800,7 +29544,7 @@
         <f>IF(F12&lt;=0.01, "PASSED (100%)", "FAILED")</f>
         <v/>
       </c>
-      <c r="I12" s="65" t="inlineStr">
+      <c r="I12" s="71" t="inlineStr">
         <is>
           <t>PASSED (100%)</t>
         </is>
@@ -29846,7 +29590,7 @@
         <f>IF(F13&lt;=0.01, "PASSED (100%)", "FAILED")</f>
         <v/>
       </c>
-      <c r="I13" s="65" t="inlineStr">
+      <c r="I13" s="71" t="inlineStr">
         <is>
           <t>PASSED (100%)</t>
         </is>
@@ -29892,7 +29636,7 @@
         <f>IF(F14&lt;=0.01, "PASSED (100%)", "FAILED")</f>
         <v/>
       </c>
-      <c r="I14" s="65" t="inlineStr">
+      <c r="I14" s="71" t="inlineStr">
         <is>
           <t>PASSED (100%)</t>
         </is>
@@ -29938,7 +29682,7 @@
         <f>IF(F15&lt;=0.01, "PASSED (100%)", "FAILED")</f>
         <v/>
       </c>
-      <c r="I15" s="65" t="inlineStr">
+      <c r="I15" s="71" t="inlineStr">
         <is>
           <t>PASSED (100%)</t>
         </is>
@@ -29984,7 +29728,7 @@
         <f>IF(F16&lt;=0.01, "PASSED (100%)", "FAILED")</f>
         <v/>
       </c>
-      <c r="I16" s="65" t="inlineStr">
+      <c r="I16" s="71" t="inlineStr">
         <is>
           <t>PASSED (100%)</t>
         </is>
